--- a/example/DEMO_HK_Answer_Key.xlsx
+++ b/example/DEMO_HK_Answer_Key.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,7 +119,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,6 +137,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1131,7 +1136,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Complete each historical schedule left-to-right in dependency order. Each schedule is one modeling concept repeated across fiscal periods. Run Check to validate every yellow cell in the workbook. Open the matching Answer Key for the formula/input and Note hint.</t>
+          <t>Complete each historical formula schedule left-to-right in dependency order. Run Check to validate the yellow formula cells. Also complete Accounting Judgment when cases are present; those responses are not graded by Check. Compare them with the matching Answer Key. Do not edit the supplied Condensed Financials classification for this Step 8A exercise.</t>
         </is>
       </c>
     </row>
@@ -13637,7 +13642,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Record the judgment on this sheet. Do not edit the supplied classification in Condensed Financials for this Step 8A exercise. Formula Check does not grade these judgment responses.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -13656,7 +13667,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Supplied model treatment</t>
+          <t>Supplied reference treatment</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -13666,17 +13677,17 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Your treatment</t>
+          <t>Treatment to defend</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Your rationale</t>
+          <t>Rationale</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>Your consequence explanation</t>
+          <t>Economic consequence</t>
         </is>
       </c>
     </row>
@@ -13704,19 +13715,19 @@
           <t>Financial Liability</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Operating Long-Term Liability</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>Lease liability concept — operating vs financial judgment</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>Operating treatment lowers NOLA/NOA; financing treatment raises Net Debt. The choice can shift RNOA versus FLEV/Spread interpretation while equity reconciliation should remain intact.</t>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>The reference model keeps the liability in operating long-term liabilities under its current lease convention. Treating it as a financial liability is also defensible when the lease obligation is viewed as debt-like financing.</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>Operating-liability treatment lowers NOLA/NOA; financial-liability treatment raises Net Debt by the same balance. Implied equity is unchanged from this classification switch alone, but RNOA versus FLEV/Spread interpretation changes.</t>
         </is>
       </c>
     </row>

--- a/example/DEMO_HK_Answer_Key.xlsx
+++ b/example/DEMO_HK_Answer_Key.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Bull" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario_Summary" sheetId="11" state="hidden" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ComponentMap" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_CheckContext" sheetId="13" state="hidden" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1136,7 +1137,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Complete each historical formula schedule left-to-right in dependency order. Run Check to validate the yellow formula cells. Also complete Accounting Judgment when cases are present; those responses are not graded by Check. Compare them with the matching Answer Key. Do not edit the supplied Condensed Financials classification for this Step 8A exercise.</t>
+          <t>Complete each historical formula schedule left-to-right in dependency order. Run Check to validate the yellow formula cells against the treatment currently selected on Accounting Judgment (blank F uses the supplied reference treatment). Also complete Accounting Judgment when cases are present; rationale and consequence responses are not graded by Check. Compare them with the matching Answer Key. Do not edit linked Condensed Financials classification cells directly.</t>
         </is>
       </c>
     </row>
@@ -11380,6 +11381,34 @@
       <c r="S119" t="inlineStr">
         <is>
           <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BAV_CHECK_CONTEXT_V1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{"base_classification_overrides":{},"judgment_bindings":[{"allowed_treatments":["Operating Long-Term Liability","Financial Liability"],"case_id":"classification::concept=lease_liability|label=operating lease liabilities","line_identity":"concept=lease_liability|label=operating lease liabilities","order":1,"override_selector":"concept:lease_liability","reference_treatment":"Operating Long-Term Liability","worksheet_row":5}],"modeled_periods":["2021-12-31","2022-12-31","2023-12-31","2024-12-31","2025-12-31"],"schema_version":1,"source_payload":{"balance_sheet":[{"concept":"","label":"Cash and cash equivalents","values":{"2021-12-31":1200.0,"2022-12-31":1350.0,"2023-12-31":1500.0,"2024-12-31":1680.0,"2025-12-31":1850.0}},{"concept":"","label":"Trade receivables","values":{"2021-12-31":850.0,"2022-12-31":920.0,"2023-12-31":1010.0,"2024-12-31":1120.0,"2025-12-31":1250.0}},{"concept":"","label":"Inventories","values":{"2021-12-31":680.0,"2022-12-31":736.0,"2023-12-31":808.0,"2024-12-31":896.0,"2025-12-31":1000.0}},{"concept":"","label":"Property, plant and equipment","values":{"2021-12-31":3200.0,"2022-12-31":3400.0,"2023-12-31":3600.0,"2024-12-31":3800.0,"2025-12-31":4000.0}},{"concept":"","label":"Goodwill","values":{"2021-12-31":900.0,"2022-12-31":900.0,"2023-12-31":900.0,"2024-12-31":900.0,"2025-12-31":900.0}},{"concept":"","label":"Other non-current assets","values":{"2021-12-31":1670.0,"2022-12-31":1894.0,"2023-12-31":2282.0,"2024-12-31":2804.0,"2025-12-31":3500.0}},{"concept":"","label":"Total assets","values":{"2021-12-31":8500.0,"2022-12-31":9200.0,"2023-12-31":10100.0,"2024-12-31":11200.0,"2025-12-31":12500.0}},{"concept":"","label":"Trade payables","values":{"2021-12-31":595.0,"2022-12-31":644.0,"2023-12-31":707.0,"2024-12-31":784.0,"2025-12-31":875.0}},{"concept":"","label":"Bank borrowings","values":{"2021-12-31":1500.0,"2022-12-31":1400.0,"2023-12-31":1300.0,"2024-12-31":1200.0,"2025-12-31":1100.0}},{"concept":"lease_liability","label":"Operating lease liabilities","values":{"2021-12-31":300.0,"2022-12-31":320.0,"2023-12-31":340.0,"2024-12-31":360.0,"2025-12-31":380.0}},{"concept":"","label":"Other non-current liabilities","values":{"2021-12-31":1005.0,"2022-12-31":1136.0,"2023-12-31":1253.0,"2024-12-31":1356.0,"2025-12-31":1445.0}},{"concept":"","label":"Total liabilities","values":{"2021-12-31":3400.0,"2022-12-31":3500.0,"2023-12-31":3600.0,"2024-12-31":3700.0,"2025-12-31":3800.0}},{"concept":"","label":"Share capital and reserves","values":{"2021-12-31":5100.0,"2022-12-31":5700.0,"2023-12-31":6500.0,"2024-12-31":7500.0,"2025-12-31":8700.0}},{"concept":"","label":"Total equity","values":{"2021-12-31":5100.0,"2022-12-31":5700.0,"2023-12-31":6500.0,"2024-12-31":7500.0,"2025-12-31":8700.0}}],"cash_flow":[{"concept":"","label":"Profit for the year","values":{"2021-12-31":2760.0,"2022-12-31":2988.0,"2023-12-31":3283.0,"2024-12-31":3644.0,"2025-12-31":4072.0}},{"concept":"","label":"Depreciation and amortisation","values":{"2021-12-31":340.0,"2022-12-31":368.0,"2023-12-31":404.0,"2024-12-31":448.0,"2025-12-31":500.0}},{"concept":"","label":"Net cash from operating activities","values":{"2021-12-31":1450.0,"2022-12-31":1600.0,"2023-12-31":1750.0,"2024-12-31":1930.0,"2025-12-31":2070.0}},{"concept":"","label":"Net cash used in investing activities","values":{"2021-12-31":-800.0,"2022-12-31":-850.0,"2023-12-31":-900.0,"2024-12-31":-950.0,"2025-12-31":-1000.0}},{"concept":"","label":"Net cash from financing activities","values":{"2021-12-31":-500.0,"2022-12-31":-600.0,"2023-12-31":-700.0,"2024-12-31":-800.0,"2025-12-31":-900.0}},{"concept":"","label":"Net change in cash and cash equivalents","values":{"2021-12-31":150.0,"2022-12-31":150.0,"2023-12-31":150.0,"2024-12-31":180.0,"2025-12-31":170.0}}],"company_name":"Demo Holdings Limited","currency":"HKD","income_statement":[{"concept":"","label":"Revenue","values":{"2021-12-31":8500.0,"2022-12-31":9200.0,"2023-12-31":10100.0,"2024-12-31":11200.0,"2025-12-31":12500.0}},{"concept":"","label":"Cost of sales","values":{"2021-12-31":-3400.0,"2022-12-31":-3680.0,"2023-12-31":-4040.0,"2024-12-31":-4480.0,"2025-12-31":-5000.0}},{"concept":"","label":"Gross profit","values":{"2021-12-31":5100.0,"2022-12-31":5520.0,"2023-12-31":6060.0,"2024-12-31":6720.0,"2025-12-31":7500.0}},{"concept":"","label":"Administrative expenses","values":{"2021-12-31":-1700.0,"2022-12-31":-1840.0,"2023-12-31":-2020.0,"2024-12-31":-2240.0,"2025-12-31":-2500.0}},{"concept":"","label":"Operating profit","values":{"2021-12-31":3400.0,"2022-12-31":3680.0,"2023-12-31":4040.0,"2024-12-31":4480.0,"2025-12-31":5000.0}},{"concept":"","label":"Finance costs","values":{"2021-12-31":-120.0,"2022-12-31":-130.0,"2023-12-31":-140.0,"2024-12-31":-150.0,"2025-12-31":-160.0}},{"concept":"","label":"Finance income","values":{"2021-12-31":45.0,"2022-12-31":50.0,"2023-12-31":55.0,"2024-12-31":60.0,"2025-12-31":65.0}},{"concept":"","label":"Profit before tax","values":{"2021-12-31":3325.0,"2022-12-31":3600.0,"2023-12-31":3955.0,"2024-12-31":4390.0,"2025-12-31":4905.0}},{"concept":"","label":"Income tax expense","values":{"2021-12-31":-565.0,"2022-12-31":-612.0,"2023-12-31":-672.0,"2024-12-31":-746.0,"2025-12-31":-833.0}},{"concept":"","label":"Profit for the year","values":{"2021-12-31":2760.0,"2022-12-31":2988.0,"2023-12-31":3283.0,"2024-12-31":3644.0,"2025-12-31":4072.0}}],"jurisdiction":"HK","periods":[{"end_date":"2021-12-31","is_interim":false,"label":"FY2021"},{"end_date":"2022-12-31","is_interim":false,"label":"FY2022"},{"end_date":"2023-12-31","is_interim":false,"label":"FY2023"},{"end_date":"2024-12-31","is_interim":false,"label":"FY2024"},{"end_date":"2025-12-31","is_interim":false,"label":"FY2025"}],"stock_code":"1234.HK","ticker":"DEMO","units":"HKD in Millions"}}</t>
         </is>
       </c>
     </row>
@@ -12556,10 +12585,9 @@
           <t>Operating lease liabilities</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Operating Long-Term Liability</t>
-        </is>
+      <c r="B14" s="12">
+        <f>IF('Accounting Judgment'!$F$5="",'Accounting Judgment'!$D$5,'Accounting Judgment'!$F$5)</f>
+        <v/>
       </c>
       <c r="C14" s="15" t="n">
         <v>300</v>
@@ -13317,7 +13345,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B15 B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Operating Working Capital Asset,Operating Working Capital Liability,Operating Long-Term Asset,Operating Long-Term Liability,Financial Asset,Financial Liability,Equity,Exclude"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13645,7 +13673,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Record the judgment on this sheet. Do not edit the supplied classification in Condensed Financials for this Step 8A exercise. Formula Check does not grade these judgment responses.</t>
+          <t>Choose a treatment in column F. That choice drives the matching Condensed Financials classification and downstream historical schedules; leaving it blank uses the supplied reference treatment. Enter your rationale and economic consequence in G:H. Formula Check grades formula cells against the treatment currently selected here; it does not grade the judgment response itself. Do not edit the linked Condensed Financials classification cell directly.</t>
         </is>
       </c>
     </row>

--- a/example/DEMO_HK_Answer_Key.xlsx
+++ b/example/DEMO_HK_Answer_Key.xlsx
@@ -1137,7 +1137,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Complete each historical formula schedule left-to-right in dependency order. Run Check to validate the yellow formula cells against the treatment currently selected on Accounting Judgment (blank F uses the supplied reference treatment). Also complete Accounting Judgment when cases are present; rationale and consequence responses are not graded by Check. Compare them with the matching Answer Key. Do not edit linked Condensed Financials classification cells directly.</t>
+          <t>Complete each historical formula schedule left-to-right in dependency order. Run Check to validate the yellow formula cells against the treatment currently selected in Accounting Judgment column F (blank F uses the supplied reference treatment). Generated Condensed Financials classification links are system-controlled and validated by Check—do not edit them or columns D:E. Also complete Accounting Judgment rationale/consequence when cases are present; those responses are not graded by Check. Compare them with the matching Answer Key.</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="B14" s="12">
-        <f>IF('Accounting Judgment'!$F$5="",'Accounting Judgment'!$D$5,'Accounting Judgment'!$F$5)</f>
+        <f>IF('Accounting Judgment'!$F$5="","Operating Long-Term Liability",'Accounting Judgment'!$F$5)</f>
         <v/>
       </c>
       <c r="C14" s="15" t="n">
@@ -13673,7 +13673,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Choose a treatment in column F. That choice drives the matching Condensed Financials classification and downstream historical schedules; leaving it blank uses the supplied reference treatment. Enter your rationale and economic consequence in G:H. Formula Check grades formula cells against the treatment currently selected here; it does not grade the judgment response itself. Do not edit the linked Condensed Financials classification cell directly.</t>
+          <t>Choose a treatment in column F only. That choice drives the matching Condensed Financials classification and downstream historical schedules; leaving F blank uses the supplied reference treatment. Columns D:E are display context and must not be edited. Enter your rationale and economic consequence in G:H. Formula Check grades formula cells against the treatment currently selected in F and validates that the generated classification links remain intact; it does not grade the judgment response itself. Do not edit the linked Condensed Financials classification cell directly.</t>
         </is>
       </c>
     </row>

--- a/example/DEMO_HK_Answer_Key.xlsx
+++ b/example/DEMO_HK_Answer_Key.xlsx
@@ -38,7 +38,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,18 +52,6 @@
     <font/>
     <font>
       <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="20"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
@@ -99,25 +87,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,26 +104,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1978,2019 +1944,2020 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Complete each historical model-construction and earnings-quality diagnostic formula schedule left-to-right in dependency order. Run Check to validate the yellow formula cells against the treatment currently selected in Accounting Judgment column F (blank F uses the supplied reference treatment). Generated Condensed Financials classification links are system-controlled and validated by Check—do not edit them or columns D:E. When Normalization Judgment is present, choose Recurring vs Non-recurring in column F (blank uses the supplied reference); Earnings Normalization formulas are checked against that choice. Also complete Accounting Judgment and Normalization Judgment rationale/consequence when cases are present; those responses are not graded by Check. Compare them with the matching Answer Key.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Period scope</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Tab</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Practice cells</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Depends on</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Revenue historical source link</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>B19:F19</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Net Income historical source link</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>B20:F20</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Effective tax rate</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>B25:F25</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Net interest</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>B26:F26</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Net interest after tax</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>B27:F27</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>effective_tax_rate_fy, net_interest_fy</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>B28:F28</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>net_income_link, net_interest_after_tax_fy</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Operating working capital assets</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>B31:F31</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Operating working capital liabilities</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>B32:F32</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Net Operating Working Capital (NOWC)</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>B33:F33</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>owca_agg, owcl_agg</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Operating long-term assets</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>B34:F34</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Operating long-term liabilities</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>B35:F35</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Net operating long-term assets (NOLA)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>B36:F36</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>olta_agg, oltl_agg</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Net Operating Assets (NOA)</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>B37:F37</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>nowc_agg, nola_agg</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Financial assets</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>B38:F38</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Financial liabilities</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>B39:F39</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>B40:F40</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>financial_assets_agg, financial_liabilities_agg</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Reformulated equity</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>B41:F41</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>noa_agg, net_debt</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Sales Growth</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>C5:F5</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>revenue_link</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>NOPAT Margin</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>B6:F6</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>nopat_fy, revenue_link</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Return on Net Operating Assets (RNOA)</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>C7:F7</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>nopat_fy, noa_agg</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>C8:F8</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>net_interest_after_tax_fy, net_debt</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Operating Spread (RNOA − After-tax CoD)</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>C9:F9</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>rnoa, after_tax_cod</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Financial leverage (FLEV)</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>C10:F10</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>net_debt, equity_reformulated_fy</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>ROE decomposition</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>C11:F11</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>rnoa, spread, flev</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Actual ROE</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>C12:F12</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>net_income_link, equity_reformulated_fy</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Pretax normalization adjustment</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Earnings Normalization</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>C9:G9</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>After-tax normalization adjustment</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Earnings Normalization</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>C11:G11</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>pretax_normalization_adjustment</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Normalized NOPAT</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Earnings Normalization</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>C12:G12</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>after_tax_normalization_adjustment</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n">
+      <c r="A33" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Normalized Net Income</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Earnings Normalization</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>C13:G13</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>after_tax_normalization_adjustment</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Operating cash flow historical source link</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Earnings Quality</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>B5:F5</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Cash conversion ratio</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>Earnings Quality</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>B7:F7</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>operating_cash_flow_link, net_income_link</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Total accruals</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>Earnings Quality</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>B8:F8</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>operating_cash_flow_link, net_income_link</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Average total assets</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Earnings Quality</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>C11:F11</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Accrual ratio</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Earnings Quality</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>C12:F12</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>total_accruals, average_total_assets</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="A39" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Operating working capital assets / Revenue</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>B11:F11</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>Operating working capital liabilities / Revenue</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>B12:F12</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="n">
+      <c r="A41" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>NOWC / Revenue</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>B13:F13</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n">
+      <c r="A42" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Change in Revenue</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>C14:F14</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n">
+      <c r="A43" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Change in NOWC</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>C15:F15</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Incremental NOWC / Change in Revenue</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>C16:F16</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="9" t="inlineStr">
         <is>
           <t>nowc_change, revenue_change</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n">
+      <c r="A45" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Change in Operating Working Capital Assets</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>C19:F19</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>owca_agg</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n">
+      <c r="A46" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Change in Operating Working Capital Liabilities</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>C20:F20</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
         <is>
           <t>owcl_agg</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="n">
+      <c r="A47" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Change in NOWC from OWCA / OWCL bridge</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>C21:F21</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>owca_change, owcl_change</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="n">
+      <c r="A48" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Incremental OWCA / Change in Revenue</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>C22:F22</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="9" t="inlineStr">
         <is>
           <t>owca_change, revenue_change</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="n">
+      <c r="A49" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>Incremental OWCL / Change in Revenue</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>C23:F23</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>owcl_change, revenue_change</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n">
+      <c r="A50" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>Average Net Operating Assets</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>C15:F15</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="9" t="inlineStr">
         <is>
           <t>noa_agg</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="n">
+      <c r="A51" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>Net Operating Asset Turnover</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>C16:F16</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>revenue_link, average_noa</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="n">
+      <c r="A52" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Net Operating Asset Intensity</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>C17:F17</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="9" t="inlineStr">
         <is>
           <t>average_noa, revenue_link</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="n">
+      <c r="A53" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>RNOA from Margin × Turnover</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>C18:F18</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>nopat_margin, noa_turnover</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="n">
+      <c r="A54" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>Change in NOPAT Margin</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>D22:F22</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F54" s="9" t="inlineStr">
         <is>
           <t>nopat_margin</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="n">
+      <c r="A55" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>Change in NOA Turnover</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>D23:F23</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>noa_turnover</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="n">
+      <c r="A56" s="9" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>Direct Change in RNOA</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>D24:F24</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="9" t="inlineStr">
         <is>
           <t>rnoa</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n">
+      <c r="A57" s="9" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>Margin Effect on Change in RNOA</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>D25:F25</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="9" t="inlineStr">
         <is>
           <t>nopat_margin_change, noa_turnover</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n">
+      <c r="A58" s="9" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>Turnover Effect on Change in RNOA</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>D26:F26</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="F58" s="9" t="inlineStr">
         <is>
           <t>noa_turnover_change, nopat_margin</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="n">
+      <c r="A59" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>Change in RNOA from Margin + Turnover Effects</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>D27:F27</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>rnoa_margin_effect, rnoa_turnover_effect</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="n">
+      <c r="A60" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>Financing Contribution to ROE</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>C31:F31</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="9" t="inlineStr">
         <is>
           <t>flev, spread</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="n">
+      <c r="A61" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>Direct Change in Decomposed ROE</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>D35:F35</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="9" t="inlineStr">
         <is>
           <t>roe_decomp</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="n">
+      <c r="A62" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>Operating Effect on Change in ROE</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>D36:F36</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="9" t="inlineStr">
         <is>
           <t>rnoa_change</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="n">
+      <c r="A63" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>Leverage Effect on Change in ROE</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>D37:F37</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr">
         <is>
           <t>flev, spread</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="n">
+      <c r="A64" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>Spread Effect on Change in ROE</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>D38:F38</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F64" s="9" t="inlineStr">
         <is>
           <t>spread, flev</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="n">
+      <c r="A65" s="9" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>Financing Effect on Change in ROE</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>D39:F39</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="9" t="inlineStr">
         <is>
           <t>leverage_effect_on_roe_change, spread_effect_on_roe_change</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="n">
+      <c r="A66" s="9" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>Change in ROE from Operating + Financing Drivers</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>D40:F40</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F66" s="9" t="inlineStr">
         <is>
           <t>operating_effect_on_roe_change, financing_effect_on_roe_change</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="n">
+      <c r="A67" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>Change in Operating Cash Flow</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr">
         <is>
           <t>Earnings Quality</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t>C15:F15</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>operating_cash_flow_link</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="n">
+      <c r="A68" s="9" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>Change in Cash Conversion Ratio</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D68" s="10" t="inlineStr">
+      <c r="D68" s="9" t="inlineStr">
         <is>
           <t>Earnings Quality</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
         <is>
           <t>C16:F16</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="F68" s="9" t="inlineStr">
         <is>
           <t>cash_conversion_ratio</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="n">
+      <c r="A69" s="9" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>Change in Total Accruals</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D69" s="9" t="inlineStr">
         <is>
           <t>Earnings Quality</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
         <is>
           <t>C17:F17</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>total_accruals</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="n">
+      <c r="A70" s="9" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>Change in Accrual Ratio</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>2023–2025 (3 cells)</t>
         </is>
       </c>
-      <c r="D70" s="10" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>Earnings Quality</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>D18:F18</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F70" s="9" t="inlineStr">
         <is>
           <t>accrual_ratio</t>
         </is>
@@ -4019,14 +3986,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Demo Holdings Limited — Earnings Quality</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Historical cash-conversion and accrual diagnostics. These are mechanical diagnostics, not an automatic quality score.</t>
         </is>
@@ -4034,354 +4001,354 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="10" t="n">
         <v>44561</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="10" t="n">
         <v>44926</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="10" t="n">
         <v>45291</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="10" t="n">
         <v>45657</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="10" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="14">
         <f>'Cash Flow Statement'!B9</f>
         <v/>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="14">
         <f>'Cash Flow Statement'!C9</f>
         <v/>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="14">
         <f>'Cash Flow Statement'!D9</f>
         <v/>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="14">
         <f>'Cash Flow Statement'!E9</f>
         <v/>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="14">
         <f>'Cash Flow Statement'!F9</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Reported Net Income</t>
         </is>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="11">
         <f>'Condensed Financials'!B20</f>
         <v/>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="11">
         <f>'Condensed Financials'!C20</f>
         <v/>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="11">
         <f>'Condensed Financials'!D20</f>
         <v/>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="11">
         <f>'Condensed Financials'!E20</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="11">
         <f>'Condensed Financials'!F20</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Cash Conversion Ratio</t>
         </is>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="15">
         <f>IF(B6=0,NA(),B5/B6)</f>
         <v/>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="15">
         <f>IF(C6=0,NA(),C5/C6)</f>
         <v/>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="15">
         <f>IF(D6=0,NA(),D5/D6)</f>
         <v/>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="15">
         <f>IF(E6=0,NA(),E5/E6)</f>
         <v/>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="15">
         <f>IF(F6=0,NA(),F5/F6)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Total Accruals (Net Income - CFO)</t>
         </is>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="14">
         <f>B6-B5</f>
         <v/>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="14">
         <f>C6-C5</f>
         <v/>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="14">
         <f>D6-D5</f>
         <v/>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="14">
         <f>E6-E5</f>
         <v/>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="14">
         <f>F6-F5</f>
         <v/>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="11">
         <f>'Balance Sheet'!B13</f>
         <v/>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="11">
         <f>'Balance Sheet'!C13</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="11">
         <f>'Balance Sheet'!D13</f>
         <v/>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="11">
         <f>'Balance Sheet'!E13</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="11">
         <f>'Balance Sheet'!F13</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Average Total Assets</t>
         </is>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="14">
         <f>(B10+C10)/2</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="14">
         <f>(C10+D10)/2</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="14">
         <f>(D10+E10)/2</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="14">
         <f>(E10+F10)/2</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Accrual Ratio</t>
         </is>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="13">
         <f>IF(C11=0,NA(),C8/C11)</f>
         <v/>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="13">
         <f>IF(D11=0,NA(),D8/D11)</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="13">
         <f>IF(E11=0,NA(),E8/E11)</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="13">
         <f>IF(F11=0,NA(),F8/F11)</f>
         <v/>
       </c>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>EARNINGS QUALITY TREND DIAGNOSTICS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Change in Operating Cash Flow</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="14">
         <f>C5-B5</f>
         <v/>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="14">
         <f>D5-C5</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="14">
         <f>E5-D5</f>
         <v/>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="14">
         <f>F5-E5</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Change in Cash Conversion Ratio</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="15">
         <f>C7-B7</f>
         <v/>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="15">
         <f>D7-C7</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="15">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="15">
         <f>F7-E7</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Change in Total Accruals</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="14">
         <f>C8-B8</f>
         <v/>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="14">
         <f>D8-C8</f>
         <v/>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="14">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="14">
         <f>F8-E8</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Change in Accrual Ratio</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="13">
         <f>D12-C12</f>
         <v/>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="13">
         <f>E12-D12</f>
         <v/>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="13">
         <f>F12-E12</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>EARNINGS QUALITY CHANGE CHECK</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="9">
         <f>IF(ABS(C17-((C6-B6)-C15))&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="9">
         <f>IF(ABS(D17-((D6-C6)-D15))&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="9">
         <f>IF(ABS(E17-((E6-D6)-E15))&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="9">
         <f>IF(ABS(F17-((F6-E6)-F15))&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
@@ -4410,21 +4377,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Working Capital Analysis</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Relate classified operating working capital to Revenue and identify how much incremental NOWC accompanies changes in sales.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>These are diagnostics, not automatic judgments. Positive Change in NOWC is an operating cash use; negative Change in NOWC is a release. Annual data alone does not prove seasonality or deterioration.</t>
         </is>
@@ -4432,473 +4399,473 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="10" t="n">
         <v>44561</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="10" t="n">
         <v>44926</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="10" t="n">
         <v>45291</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="10" t="n">
         <v>45657</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="10" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <f>'Condensed Financials'!B19</f>
         <v/>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="11">
         <f>'Condensed Financials'!C19</f>
         <v/>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="11">
         <f>'Condensed Financials'!D19</f>
         <v/>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="11">
         <f>'Condensed Financials'!E19</f>
         <v/>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="11">
         <f>'Condensed Financials'!F19</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Operating Working Capital Assets</t>
         </is>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="11">
         <f>'Condensed Financials'!B31</f>
         <v/>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="11">
         <f>'Condensed Financials'!C31</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="11">
         <f>'Condensed Financials'!D31</f>
         <v/>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="11">
         <f>'Condensed Financials'!E31</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="11">
         <f>'Condensed Financials'!F31</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Operating Working Capital Liabilities</t>
         </is>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="11">
         <f>'Condensed Financials'!B32</f>
         <v/>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="11">
         <f>'Condensed Financials'!C32</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="11">
         <f>'Condensed Financials'!D32</f>
         <v/>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="11">
         <f>'Condensed Financials'!E32</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="11">
         <f>'Condensed Financials'!F32</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>NOWC</t>
         </is>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <f>'Condensed Financials'!B33</f>
         <v/>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="11">
         <f>'Condensed Financials'!C33</f>
         <v/>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="11">
         <f>'Condensed Financials'!D33</f>
         <v/>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="11">
         <f>'Condensed Financials'!E33</f>
         <v/>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="11">
         <f>'Condensed Financials'!F33</f>
         <v/>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>OWCA / Revenue</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="13">
         <f>IF(B6=0,NA(),B7/B6)</f>
         <v/>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="13">
         <f>IF(C6=0,NA(),C7/C6)</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="13">
         <f>IF(D6=0,NA(),D7/D6)</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="13">
         <f>IF(E6=0,NA(),E7/E6)</f>
         <v/>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="13">
         <f>IF(F6=0,NA(),F7/F6)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>OWCL / Revenue</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="13">
         <f>IF(B6=0,NA(),B8/B6)</f>
         <v/>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="13">
         <f>IF(C6=0,NA(),C8/C6)</f>
         <v/>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="13">
         <f>IF(D6=0,NA(),D8/D6)</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="13">
         <f>IF(E6=0,NA(),E8/E6)</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="13">
         <f>IF(F6=0,NA(),F8/F6)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>NOWC / Revenue</t>
         </is>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="13">
         <f>IF(B6=0,NA(),B9/B6)</f>
         <v/>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="13">
         <f>IF(C6=0,NA(),C9/C6)</f>
         <v/>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="13">
         <f>IF(D6=0,NA(),D9/D6)</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="13">
         <f>IF(E6=0,NA(),E9/E6)</f>
         <v/>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="13">
         <f>IF(F6=0,NA(),F9/F6)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Change in Revenue</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="14">
         <f>C6-B6</f>
         <v/>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="14">
         <f>D6-C6</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="14">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="14">
         <f>F6-E6</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Change in NOWC</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="14">
         <f>C9-B9</f>
         <v/>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="14">
         <f>D9-C9</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="14">
         <f>E9-D9</f>
         <v/>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="14">
         <f>F9-E9</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Incremental NOWC / Change in Revenue</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="13">
         <f>IF(C14=0,NA(),C15/C14)</f>
         <v/>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="13">
         <f>IF(D14=0,NA(),D15/D14)</f>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="13">
         <f>IF(E14=0,NA(),E15/E14)</f>
         <v/>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="13">
         <f>IF(F14=0,NA(),F15/F14)</f>
         <v/>
       </c>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>WORKING-CAPITAL DRIVER DECOMPOSITION</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Change in OWCA</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="14">
         <f>C7-B7</f>
         <v/>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="14">
         <f>D7-C7</f>
         <v/>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="14">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="14">
         <f>F7-E7</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Change in OWCL</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="14">
         <f>C8-B8</f>
         <v/>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="14">
         <f>D8-C8</f>
         <v/>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="14">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="14">
         <f>F8-E8</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Change in NOWC from Components</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="14">
         <f>C19-C20</f>
         <v/>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="14">
         <f>D19-D20</f>
         <v/>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="14">
         <f>E19-E20</f>
         <v/>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="14">
         <f>F19-F20</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Incremental OWCA / Change in Revenue</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="13">
         <f>IF(C14=0,NA(),C19/C14)</f>
         <v/>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="13">
         <f>IF(D14=0,NA(),D19/D14)</f>
         <v/>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="13">
         <f>IF(E14=0,NA(),E19/E14)</f>
         <v/>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="13">
         <f>IF(F14=0,NA(),F19/F14)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Incremental OWCL / Change in Revenue</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="13">
         <f>IF(C14=0,NA(),C20/C14)</f>
         <v/>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="13">
         <f>IF(D14=0,NA(),D20/D14)</f>
         <v/>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="13">
         <f>IF(E14=0,NA(),E20/E14)</f>
         <v/>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="13">
         <f>IF(F14=0,NA(),F20/F14)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>DRIVER DECOMPOSITION CHECK</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="9">
         <f>IF(ABS(C21-C15)&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="9">
         <f>IF(ABS(D21-D15)&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="9">
         <f>IF(ABS(E21-E15)&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="9">
         <f>IF(ABS(F21-F15)&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
@@ -4919,7 +4886,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Deferred from historical-only v1</t>
         </is>
@@ -4940,7 +4907,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Deferred from historical-only v1</t>
         </is>
@@ -4961,7 +4928,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Deferred from historical-only v1</t>
         </is>
@@ -4982,7 +4949,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Deferred from historical-only v1</t>
         </is>
@@ -27314,28 +27281,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Company: Demo Holdings Limited (DEMO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Statement: Income Statement</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Units: HKD in Millions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Source: manual ingestion (HK)</t>
         </is>
@@ -27343,266 +27310,266 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="10" t="n">
         <v>44561</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="10" t="n">
         <v>44926</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="10" t="n">
         <v>45291</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="10" t="n">
         <v>45657</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="10" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="11" t="n">
         <v>8500</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="11" t="n">
         <v>9200</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="11" t="n">
         <v>10100</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="11" t="n">
         <v>11200</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="11" t="n">
         <v>12500</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Cost of sales</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="11" t="n">
         <v>-3400</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="11" t="n">
         <v>-3680</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="11" t="n">
         <v>-4040</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="11" t="n">
         <v>-4480</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="11" t="n">
         <v>-5000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="11" t="n">
         <v>5100</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="11" t="n">
         <v>5520</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="11" t="n">
         <v>6060</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="11" t="n">
         <v>6720</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="11" t="n">
         <v>7500</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Administrative expenses</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="11" t="n">
         <v>-1700</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="11" t="n">
         <v>-1840</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="11" t="n">
         <v>-1820</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="11" t="n">
         <v>-2240</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="11" t="n">
         <v>-2500</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Restructuring expense</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="11" t="n">
         <v>-200</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Operating profit</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="11" t="n">
         <v>3400</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="11" t="n">
         <v>3680</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="11" t="n">
         <v>4040</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="11" t="n">
         <v>4480</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="11" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Finance costs</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="11" t="n">
         <v>-120</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="11" t="n">
         <v>-130</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="11" t="n">
         <v>-140</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="11" t="n">
         <v>-150</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="11" t="n">
         <v>-160</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Finance income</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="11" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="11" t="n">
         <v>3325</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="11" t="n">
         <v>3600</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="11" t="n">
         <v>3955</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="11" t="n">
         <v>4390</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="11" t="n">
         <v>4905</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Income tax expense</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="11" t="n">
         <v>-565</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="11" t="n">
         <v>-612</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="11" t="n">
         <v>-672</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="11" t="n">
         <v>-746</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="11" t="n">
         <v>-833</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="11" t="n">
         <v>2760</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="11" t="n">
         <v>2988</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="11" t="n">
         <v>3283</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="11" t="n">
         <v>3644</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="11" t="n">
         <v>4072</v>
       </c>
     </row>
@@ -27629,28 +27596,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Company: Demo Holdings Limited (DEMO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Statement: Balance Sheet</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Units: HKD in Millions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Source: manual ingestion (HK)</t>
         </is>
@@ -27658,332 +27625,332 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="10" t="n">
         <v>44561</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="10" t="n">
         <v>44926</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="10" t="n">
         <v>45291</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="10" t="n">
         <v>45657</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="10" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="11" t="n">
         <v>1200</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="11" t="n">
         <v>1350</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="11" t="n">
         <v>1500</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="11" t="n">
         <v>1680</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="11" t="n">
         <v>1850</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Trade receivables</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="11" t="n">
         <v>850</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="11" t="n">
         <v>920</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="11" t="n">
         <v>1010</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="11" t="n">
         <v>1120</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="11" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="11" t="n">
         <v>680</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="11" t="n">
         <v>736</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="11" t="n">
         <v>808</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="11" t="n">
         <v>896</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="11" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="11" t="n">
         <v>3200</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="11" t="n">
         <v>3400</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="11" t="n">
         <v>3600</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="11" t="n">
         <v>3800</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="11" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="11" t="n">
         <v>900</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="11" t="n">
         <v>900</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="11" t="n">
         <v>900</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="11" t="n">
         <v>900</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="11" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Other non-current assets</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="11" t="n">
         <v>1670</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="11" t="n">
         <v>1894</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="11" t="n">
         <v>2282</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="11" t="n">
         <v>2804</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="11" t="n">
         <v>3500</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="11" t="n">
         <v>8500</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="11" t="n">
         <v>9200</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="11" t="n">
         <v>10100</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="11" t="n">
         <v>11200</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="11" t="n">
         <v>12500</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Trade payables</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="11" t="n">
         <v>595</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="11" t="n">
         <v>644</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="11" t="n">
         <v>707</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="11" t="n">
         <v>784</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="11" t="n">
         <v>875</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Bank borrowings</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="11" t="n">
         <v>1500</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="11" t="n">
         <v>1400</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="11" t="n">
         <v>1300</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="11" t="n">
         <v>1200</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="11" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Operating lease liabilities</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="11" t="n">
         <v>320</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="11" t="n">
         <v>340</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="11" t="n">
         <v>360</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="11" t="n">
         <v>380</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Other non-current liabilities</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="11" t="n">
         <v>1005</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="11" t="n">
         <v>1136</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="11" t="n">
         <v>1253</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="11" t="n">
         <v>1356</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="11" t="n">
         <v>1445</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="11" t="n">
         <v>3400</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="11" t="n">
         <v>3500</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="11" t="n">
         <v>3600</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="11" t="n">
         <v>3700</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="11" t="n">
         <v>3800</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Share capital and reserves</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="11" t="n">
         <v>5100</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="11" t="n">
         <v>5700</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="11" t="n">
         <v>6500</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="11" t="n">
         <v>7500</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="11" t="n">
         <v>8700</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="11" t="n">
         <v>5100</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="11" t="n">
         <v>5700</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="11" t="n">
         <v>6500</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="11" t="n">
         <v>7500</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="11" t="n">
         <v>8700</v>
       </c>
     </row>
@@ -28010,28 +27977,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Company: Demo Holdings Limited (DEMO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Statement: Cash Flow Statement</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Units: HKD in Millions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Source: manual ingestion (HK)</t>
         </is>
@@ -28039,156 +28006,156 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="10" t="n">
         <v>44561</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="10" t="n">
         <v>44926</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="10" t="n">
         <v>45291</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="10" t="n">
         <v>45657</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="10" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="11" t="n">
         <v>2760</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="11" t="n">
         <v>2988</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="11" t="n">
         <v>3283</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="11" t="n">
         <v>3644</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="11" t="n">
         <v>4072</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="11" t="n">
         <v>340</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="11" t="n">
         <v>368</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="11" t="n">
         <v>404</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="11" t="n">
         <v>448</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="11" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="11" t="n">
         <v>1450</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="11" t="n">
         <v>1600</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="11" t="n">
         <v>1750</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="11" t="n">
         <v>1930</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="11" t="n">
         <v>2070</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Net cash used in investing activities</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="11" t="n">
         <v>-800</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="11" t="n">
         <v>-850</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="11" t="n">
         <v>-900</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="11" t="n">
         <v>-950</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="11" t="n">
         <v>-1000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Net cash from financing activities</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="11" t="n">
         <v>-500</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="11" t="n">
         <v>-600</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="11" t="n">
         <v>-700</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="11" t="n">
         <v>-800</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="11" t="n">
         <v>-900</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Net change in cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="11" t="n">
         <v>180</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="11" t="n">
         <v>170</v>
       </c>
     </row>
@@ -28217,7 +28184,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Demo Holdings Limited (DEMO) — Condensed Financials</t>
         </is>
@@ -28226,1020 +28193,1020 @@
     <row r="2"/>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>BALANCE SHEET CLASSIFICATION</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="10" t="n">
         <v>44561</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="10" t="n">
         <v>44926</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="10" t="n">
         <v>45291</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="10" t="n">
         <v>45657</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Financial Asset</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="11" t="n">
         <v>1200</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="11" t="n">
         <v>1350</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="11" t="n">
         <v>1500</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="11" t="n">
         <v>1680</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="11" t="n">
         <v>1850</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Trade receivables</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Operating Working Capital Asset</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="11" t="n">
         <v>850</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="11" t="n">
         <v>920</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="11" t="n">
         <v>1010</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="11" t="n">
         <v>1120</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="11" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Operating Working Capital Asset</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="11" t="n">
         <v>680</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="11" t="n">
         <v>736</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="11" t="n">
         <v>808</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="11" t="n">
         <v>896</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="11" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Operating Long-Term Asset</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="11" t="n">
         <v>3200</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="11" t="n">
         <v>3400</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="11" t="n">
         <v>3600</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="11" t="n">
         <v>3800</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="11" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Operating Long-Term Asset</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="11" t="n">
         <v>900</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="11" t="n">
         <v>900</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="11" t="n">
         <v>900</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="11" t="n">
         <v>900</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="11" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Other non-current assets</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Operating Long-Term Asset</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="11" t="n">
         <v>1670</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="11" t="n">
         <v>1894</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="11" t="n">
         <v>2282</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="11" t="n">
         <v>2804</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="11" t="n">
         <v>3500</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Trade payables</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Operating Working Capital Liability</t>
         </is>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="11" t="n">
         <v>595</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="11" t="n">
         <v>644</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="11" t="n">
         <v>707</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="11" t="n">
         <v>784</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="11" t="n">
         <v>875</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Bank borrowings</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Financial Liability</t>
         </is>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="11" t="n">
         <v>1500</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="11" t="n">
         <v>1400</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="11" t="n">
         <v>1300</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="11" t="n">
         <v>1200</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="11" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Operating lease liabilities</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="9">
         <f>IF('Accounting Judgment'!$F$5="","Operating Long-Term Liability",'Accounting Judgment'!$F$5)</f>
         <v/>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="11" t="n">
         <v>320</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="11" t="n">
         <v>340</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="11" t="n">
         <v>360</v>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="11" t="n">
         <v>380</v>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>⚠ Review: Lease liability concept — operating vs financial judgment</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Other non-current liabilities</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Operating Long-Term Liability</t>
         </is>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="11" t="n">
         <v>1005</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="11" t="n">
         <v>1136</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="11" t="n">
         <v>1253</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="11" t="n">
         <v>1356</v>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="11" t="n">
         <v>1445</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Share capital and reserves</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="11" t="n">
         <v>5100</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="11" t="n">
         <v>5700</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="11" t="n">
         <v>6500</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="11" t="n">
         <v>7500</v>
       </c>
-      <c r="G16" s="16" t="n">
+      <c r="G16" s="11" t="n">
         <v>8700</v>
       </c>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>CONDENSED INCOME STATEMENT</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="10" t="n">
         <v>44561</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="10" t="n">
         <v>44926</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="10" t="n">
         <v>45291</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="10" t="n">
         <v>45657</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="10" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="12">
         <f>'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="12">
         <f>'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="12">
         <f>'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="12">
         <f>'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="12">
         <f>'Income Statement'!F7</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="12">
         <f>'Income Statement'!B17</f>
         <v/>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="12">
         <f>'Income Statement'!C17</f>
         <v/>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="12">
         <f>'Income Statement'!D17</f>
         <v/>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="12">
         <f>'Income Statement'!E17</f>
         <v/>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="12">
         <f>'Income Statement'!F17</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="9">
         <f>'Income Statement'!B15</f>
         <v/>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="9">
         <f>'Income Statement'!C15</f>
         <v/>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="9">
         <f>'Income Statement'!D15</f>
         <v/>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="9">
         <f>'Income Statement'!E15</f>
         <v/>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="9">
         <f>'Income Statement'!F15</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Tax Expense</t>
         </is>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="9">
         <f>'Income Statement'!B16</f>
         <v/>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="9">
         <f>'Income Statement'!C16</f>
         <v/>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="9">
         <f>'Income Statement'!D16</f>
         <v/>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="9">
         <f>'Income Statement'!E16</f>
         <v/>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="9">
         <f>'Income Statement'!F16</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="9">
         <f>'Income Statement'!B13</f>
         <v/>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="9">
         <f>'Income Statement'!C13</f>
         <v/>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="9">
         <f>'Income Statement'!D13</f>
         <v/>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="9">
         <f>'Income Statement'!E13</f>
         <v/>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="9">
         <f>'Income Statement'!F13</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="9">
         <f>'Income Statement'!B14</f>
         <v/>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="9">
         <f>'Income Statement'!C14</f>
         <v/>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="9">
         <f>'Income Statement'!D14</f>
         <v/>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="9">
         <f>'Income Statement'!E14</f>
         <v/>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="9">
         <f>'Income Statement'!F14</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Effective Tax Rate</t>
         </is>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="13">
         <f>IF(B21=0,NA(),-B22/B21)</f>
         <v/>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="13">
         <f>IF(C21=0,NA(),-C22/C21)</f>
         <v/>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="13">
         <f>IF(D21=0,NA(),-D22/D21)</f>
         <v/>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="13">
         <f>IF(E21=0,NA(),-E22/E21)</f>
         <v/>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="13">
         <f>IF(F21=0,NA(),-F22/F21)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Net Interest</t>
         </is>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="14">
         <f>-(B23+B24)</f>
         <v/>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="14">
         <f>-(C23+C24)</f>
         <v/>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="14">
         <f>-(D23+D24)</f>
         <v/>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="14">
         <f>-(E23+E24)</f>
         <v/>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="14">
         <f>-(F23+F24)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Net Interest After Tax</t>
         </is>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="14">
         <f>IF(B26=0,0,IF(ISNA(B25),NA(),B26*(1-B25)))</f>
         <v/>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="14">
         <f>IF(C26=0,0,IF(ISNA(C25),NA(),C26*(1-C25)))</f>
         <v/>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="14">
         <f>IF(D26=0,0,IF(ISNA(D25),NA(),D26*(1-D25)))</f>
         <v/>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="14">
         <f>IF(E26=0,0,IF(ISNA(E25),NA(),E26*(1-E25)))</f>
         <v/>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="14">
         <f>IF(F26=0,0,IF(ISNA(F25),NA(),F26*(1-F25)))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B28" s="22">
+      <c r="B28" s="14">
         <f>B20+B27</f>
         <v/>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="14">
         <f>C20+C27</f>
         <v/>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="14">
         <f>D20+D27</f>
         <v/>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="14">
         <f>E20+E27</f>
         <v/>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="14">
         <f>F20+F27</f>
         <v/>
       </c>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>CONDENSED BALANCE SHEET</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Operating Working Capital Assets</t>
         </is>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",C$6:C$16)</f>
         <v/>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",D$6:D$16)</f>
         <v/>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",E$6:E$16)</f>
         <v/>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",F$6:F$16)</f>
         <v/>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",G$6:G$16)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Operating Working Capital Liabilities</t>
         </is>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",C$6:C$16)</f>
         <v/>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",D$6:D$16)</f>
         <v/>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",E$6:E$16)</f>
         <v/>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",F$6:F$16)</f>
         <v/>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",G$6:G$16)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>NOWC</t>
         </is>
       </c>
-      <c r="B33" s="22">
+      <c r="B33" s="14">
         <f>B31-B32</f>
         <v/>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="14">
         <f>C31-C32</f>
         <v/>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="14">
         <f>D31-D32</f>
         <v/>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="14">
         <f>E31-E32</f>
         <v/>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="14">
         <f>F31-F32</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Operating Long-Term Assets</t>
         </is>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",C$6:C$16)</f>
         <v/>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",D$6:D$16)</f>
         <v/>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",E$6:E$16)</f>
         <v/>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",F$6:F$16)</f>
         <v/>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",G$6:G$16)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Operating Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",C$6:C$16)</f>
         <v/>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",D$6:D$16)</f>
         <v/>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",E$6:E$16)</f>
         <v/>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",F$6:F$16)</f>
         <v/>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="14">
         <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",G$6:G$16)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>NOLA</t>
         </is>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="14">
         <f>B34-B35</f>
         <v/>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="14">
         <f>C34-C35</f>
         <v/>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="14">
         <f>D34-D35</f>
         <v/>
       </c>
-      <c r="E36" s="22">
+      <c r="E36" s="14">
         <f>E34-E35</f>
         <v/>
       </c>
-      <c r="F36" s="22">
+      <c r="F36" s="14">
         <f>F34-F35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="B37" s="22">
+      <c r="B37" s="14">
         <f>B33+B36</f>
         <v/>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="14">
         <f>C33+C36</f>
         <v/>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="14">
         <f>D33+D36</f>
         <v/>
       </c>
-      <c r="E37" s="22">
+      <c r="E37" s="14">
         <f>E33+E36</f>
         <v/>
       </c>
-      <c r="F37" s="22">
+      <c r="F37" s="14">
         <f>F33+F36</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Financial Assets</t>
         </is>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="14">
         <f>SUMIF($B$6:$B$16,"Financial Asset",C$6:C$16)</f>
         <v/>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="14">
         <f>SUMIF($B$6:$B$16,"Financial Asset",D$6:D$16)</f>
         <v/>
       </c>
-      <c r="D38" s="20">
+      <c r="D38" s="14">
         <f>SUMIF($B$6:$B$16,"Financial Asset",E$6:E$16)</f>
         <v/>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="14">
         <f>SUMIF($B$6:$B$16,"Financial Asset",F$6:F$16)</f>
         <v/>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="14">
         <f>SUMIF($B$6:$B$16,"Financial Asset",G$6:G$16)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Financial Liabilities</t>
         </is>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="14">
         <f>SUMIF($B$6:$B$16,"Financial Liability",C$6:C$16)</f>
         <v/>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="14">
         <f>SUMIF($B$6:$B$16,"Financial Liability",D$6:D$16)</f>
         <v/>
       </c>
-      <c r="D39" s="20">
+      <c r="D39" s="14">
         <f>SUMIF($B$6:$B$16,"Financial Liability",E$6:E$16)</f>
         <v/>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="14">
         <f>SUMIF($B$6:$B$16,"Financial Liability",F$6:F$16)</f>
         <v/>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="14">
         <f>SUMIF($B$6:$B$16,"Financial Liability",G$6:G$16)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="14">
         <f>B39-B38</f>
         <v/>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="14">
         <f>C39-C38</f>
         <v/>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="14">
         <f>D39-D38</f>
         <v/>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="14">
         <f>E39-E38</f>
         <v/>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="14">
         <f>F39-F38</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Equity (NOA - Net Debt)</t>
         </is>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="14">
         <f>B37-B40</f>
         <v/>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="14">
         <f>C37-C40</f>
         <v/>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="14">
         <f>D37-D40</f>
         <v/>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="14">
         <f>E37-E40</f>
         <v/>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="14">
         <f>F37-F40</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Reported Equity</t>
         </is>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="11">
         <f>'Balance Sheet'!B20</f>
         <v/>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="11">
         <f>'Balance Sheet'!C20</f>
         <v/>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="11">
         <f>'Balance Sheet'!D20</f>
         <v/>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="11">
         <f>'Balance Sheet'!E20</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="11">
         <f>'Balance Sheet'!F20</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Total Capital</t>
         </is>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="11">
         <f>B40+B41</f>
         <v/>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="11">
         <f>C40+C41</f>
         <v/>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="11">
         <f>D40+D41</f>
         <v/>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="11">
         <f>E40+E41</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="11">
         <f>F40+F41</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="9">
         <f>IF(ABS(B41-B42)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="9">
         <f>IF(ABS(C41-C42)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="9">
         <f>IF(ABS(D41-D42)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="9">
         <f>IF(ABS(E41-E42)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="9">
         <f>IF(ABS(F41-F42)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
@@ -29273,14 +29240,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Demo Holdings Limited — DuPont Decomposition</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ROE = RNOA + FLEV × Spread</t>
         </is>
@@ -29288,880 +29255,880 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="10" t="n">
         <v>44561</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="10" t="n">
         <v>44926</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="10" t="n">
         <v>45291</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="10" t="n">
         <v>45657</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="10" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Sales Growth</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="13">
         <f>IF('Condensed Financials'!B19=0,NA(),'Condensed Financials'!C19/'Condensed Financials'!B19-1)</f>
         <v/>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="13">
         <f>IF('Condensed Financials'!C19=0,NA(),'Condensed Financials'!D19/'Condensed Financials'!C19-1)</f>
         <v/>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="13">
         <f>IF('Condensed Financials'!D19=0,NA(),'Condensed Financials'!E19/'Condensed Financials'!D19-1)</f>
         <v/>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="13">
         <f>IF('Condensed Financials'!E19=0,NA(),'Condensed Financials'!F19/'Condensed Financials'!E19-1)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>NOPAT Margin</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="13">
         <f>IF('Condensed Financials'!B19=0,NA(),'Condensed Financials'!B28/'Condensed Financials'!B19)</f>
         <v/>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="13">
         <f>IF('Condensed Financials'!C19=0,NA(),'Condensed Financials'!C28/'Condensed Financials'!C19)</f>
         <v/>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="13">
         <f>IF('Condensed Financials'!D19=0,NA(),'Condensed Financials'!D28/'Condensed Financials'!D19)</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="13">
         <f>IF('Condensed Financials'!E19=0,NA(),'Condensed Financials'!E28/'Condensed Financials'!E19)</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="13">
         <f>IF('Condensed Financials'!F19=0,NA(),'Condensed Financials'!F28/'Condensed Financials'!F19)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>RNOA</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="13">
         <f>IF((('Condensed Financials'!C37+'Condensed Financials'!B37)/2)=0,NA(),'Condensed Financials'!C28/(('Condensed Financials'!C37+'Condensed Financials'!B37)/2))</f>
         <v/>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="13">
         <f>IF((('Condensed Financials'!D37+'Condensed Financials'!C37)/2)=0,NA(),'Condensed Financials'!D28/(('Condensed Financials'!D37+'Condensed Financials'!C37)/2))</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="13">
         <f>IF((('Condensed Financials'!E37+'Condensed Financials'!D37)/2)=0,NA(),'Condensed Financials'!E28/(('Condensed Financials'!E37+'Condensed Financials'!D37)/2))</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="13">
         <f>IF((('Condensed Financials'!F37+'Condensed Financials'!E37)/2)=0,NA(),'Condensed Financials'!F28/(('Condensed Financials'!F37+'Condensed Financials'!E37)/2))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>After-tax CoD</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="13">
         <f>IF((('Condensed Financials'!C40+'Condensed Financials'!B40)/2)=0,NA(),'Condensed Financials'!C27/(('Condensed Financials'!C40+'Condensed Financials'!B40)/2))</f>
         <v/>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="13">
         <f>IF((('Condensed Financials'!D40+'Condensed Financials'!C40)/2)=0,NA(),'Condensed Financials'!D27/(('Condensed Financials'!D40+'Condensed Financials'!C40)/2))</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="13">
         <f>IF((('Condensed Financials'!E40+'Condensed Financials'!D40)/2)=0,NA(),'Condensed Financials'!E27/(('Condensed Financials'!E40+'Condensed Financials'!D40)/2))</f>
         <v/>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="13">
         <f>IF((('Condensed Financials'!F40+'Condensed Financials'!E40)/2)=0,NA(),'Condensed Financials'!F27/(('Condensed Financials'!F40+'Condensed Financials'!E40)/2))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="13">
         <f>C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="13">
         <f>D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="13">
         <f>E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="13">
         <f>F7-F8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>FLEV</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="12">
         <f>IF((('Condensed Financials'!C41+'Condensed Financials'!B41)/2)=0,NA(),(('Condensed Financials'!C40+'Condensed Financials'!B40)/2)/(('Condensed Financials'!C41+'Condensed Financials'!B41)/2))</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="12">
         <f>IF((('Condensed Financials'!D41+'Condensed Financials'!C41)/2)=0,NA(),(('Condensed Financials'!D40+'Condensed Financials'!C40)/2)/(('Condensed Financials'!D41+'Condensed Financials'!C41)/2))</f>
         <v/>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="12">
         <f>IF((('Condensed Financials'!E41+'Condensed Financials'!D41)/2)=0,NA(),(('Condensed Financials'!E40+'Condensed Financials'!D40)/2)/(('Condensed Financials'!E41+'Condensed Financials'!D41)/2))</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="12">
         <f>IF((('Condensed Financials'!F41+'Condensed Financials'!E41)/2)=0,NA(),(('Condensed Financials'!F40+'Condensed Financials'!E40)/2)/(('Condensed Financials'!F41+'Condensed Financials'!E41)/2))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>ROE (decomposed)</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="13">
         <f>C7+C10*(C9)</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="13">
         <f>D7+D10*(D9)</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="13">
         <f>E7+E10*(E9)</f>
         <v/>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="13">
         <f>F7+F10*(F9)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Actual ROE</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="13">
         <f>IF((('Condensed Financials'!C41+'Condensed Financials'!B41)/2)=0,NA(),'Condensed Financials'!C20/(('Condensed Financials'!C41+'Condensed Financials'!B41)/2))</f>
         <v/>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="13">
         <f>IF((('Condensed Financials'!D41+'Condensed Financials'!C41)/2)=0,NA(),'Condensed Financials'!D20/(('Condensed Financials'!D41+'Condensed Financials'!C41)/2))</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="13">
         <f>IF((('Condensed Financials'!E41+'Condensed Financials'!D41)/2)=0,NA(),'Condensed Financials'!E20/(('Condensed Financials'!E41+'Condensed Financials'!D41)/2))</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="13">
         <f>IF((('Condensed Financials'!F41+'Condensed Financials'!E41)/2)=0,NA(),'Condensed Financials'!F20/(('Condensed Financials'!F41+'Condensed Financials'!E41)/2))</f>
         <v/>
       </c>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>RNOA DRIVER DECOMPOSITION</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Average NOA</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="14">
         <f>('Condensed Financials'!B37+'Condensed Financials'!C37)/2</f>
         <v/>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="14">
         <f>('Condensed Financials'!C37+'Condensed Financials'!D37)/2</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="14">
         <f>('Condensed Financials'!D37+'Condensed Financials'!E37)/2</f>
         <v/>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="14">
         <f>('Condensed Financials'!E37+'Condensed Financials'!F37)/2</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>NOA Turnover</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="15">
         <f>IF(C15=0,NA(),'Condensed Financials'!C19/C15)</f>
         <v/>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="15">
         <f>IF(D15=0,NA(),'Condensed Financials'!D19/D15)</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="15">
         <f>IF(E15=0,NA(),'Condensed Financials'!E19/E15)</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="15">
         <f>IF(F15=0,NA(),'Condensed Financials'!F19/F15)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>NOA Intensity</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="15">
         <f>IF('Condensed Financials'!C19=0,NA(),C15/'Condensed Financials'!C19)</f>
         <v/>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="15">
         <f>IF('Condensed Financials'!D19=0,NA(),D15/'Condensed Financials'!D19)</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="15">
         <f>IF('Condensed Financials'!E19=0,NA(),E15/'Condensed Financials'!E19)</f>
         <v/>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="15">
         <f>IF('Condensed Financials'!F19=0,NA(),F15/'Condensed Financials'!F19)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>RNOA from Margin × Turnover</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="13">
         <f>C6*C16</f>
         <v/>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="13">
         <f>D6*D16</f>
         <v/>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="13">
         <f>E6*E16</f>
         <v/>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="13">
         <f>F6*F16</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>RNOA DRIVER CHECK</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="9">
         <f>IF(ISNA(C18),"N/A",IF(ISNA(C7),"CHECK",IF(ABS(C18-C7)&lt;0.0000001,"OK","CHECK")))</f>
         <v/>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="9">
         <f>IF(ISNA(D18),"N/A",IF(ISNA(D7),"CHECK",IF(ABS(D18-D7)&lt;0.0000001,"OK","CHECK")))</f>
         <v/>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="9">
         <f>IF(ISNA(E18),"N/A",IF(ISNA(E7),"CHECK",IF(ABS(E18-E7)&lt;0.0000001,"OK","CHECK")))</f>
         <v/>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="9">
         <f>IF(ISNA(F18),"N/A",IF(ISNA(F7),"CHECK",IF(ABS(F18-F7)&lt;0.0000001,"OK","CHECK")))</f>
         <v/>
       </c>
     </row>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>RNOA CHANGE ATTRIBUTION</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Change in NOPAT Margin</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="13">
         <f>D6-C6</f>
         <v/>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="13">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="13">
         <f>F6-E6</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Change in NOA Turnover</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="15">
         <f>D16-C16</f>
         <v/>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="15">
         <f>E16-D16</f>
         <v/>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="15">
         <f>F16-E16</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Direct Change in RNOA</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="13">
         <f>D7-C7</f>
         <v/>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="13">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="13">
         <f>F7-E7</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Margin Effect on RNOA Change</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="13">
         <f>D22*((D16+C16)/2)</f>
         <v/>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="13">
         <f>E22*((E16+D16)/2)</f>
         <v/>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="13">
         <f>F22*((F16+E16)/2)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Turnover Effect on RNOA Change</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="13">
         <f>D23*((D6+C6)/2)</f>
         <v/>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="13">
         <f>E23*((E6+D6)/2)</f>
         <v/>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="13">
         <f>F23*((F6+E6)/2)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>RNOA Change from Drivers</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="13">
         <f>D25+D26</f>
         <v/>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="13">
         <f>E25+E26</f>
         <v/>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="13">
         <f>F25+F26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>RNOA CHANGE DRIVER CHECK</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="9">
         <f>IF(OR(ISNA(D27),ISNA(D24)),"N/A",IF(ABS(D27-D24)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="9">
         <f>IF(OR(ISNA(E27),ISNA(E24)),"N/A",IF(ABS(E27-E24)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="9">
         <f>IF(OR(ISNA(F27),ISNA(F24)),"N/A",IF(ABS(F27-F24)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>ROE OPERATING / FINANCING ATTRIBUTION</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Financing Contribution to ROE</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="13">
         <f>C10*C9</f>
         <v/>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="13">
         <f>D10*D9</f>
         <v/>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="13">
         <f>E10*E9</f>
         <v/>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="13">
         <f>F10*F9</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>ROE LEVEL ATTRIBUTION CHECK</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="9">
         <f>IF(OR(ISNA(C7),ISNA(C31),ISNA(C11)),"N/A",IF(ABS(C7+C31-C11)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="9">
         <f>IF(OR(ISNA(D7),ISNA(D31),ISNA(D11)),"N/A",IF(ABS(D7+D31-D11)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="9">
         <f>IF(OR(ISNA(E7),ISNA(E31),ISNA(E11)),"N/A",IF(ABS(E7+E31-E11)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="9">
         <f>IF(OR(ISNA(F7),ISNA(F31),ISNA(F11)),"N/A",IF(ABS(F7+F31-F11)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
     </row>
     <row r="33"/>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>ROE CHANGE ATTRIBUTION</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Direct Change in Decomposed ROE</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="13">
         <f>D11-C11</f>
         <v/>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="13">
         <f>E11-D11</f>
         <v/>
       </c>
-      <c r="F35" s="19">
+      <c r="F35" s="13">
         <f>F11-E11</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Operating Effect on Change in ROE</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="13">
         <f>D24</f>
         <v/>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="13">
         <f>E24</f>
         <v/>
       </c>
-      <c r="F36" s="19">
+      <c r="F36" s="13">
         <f>F24</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Leverage Effect on Change in ROE</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="13">
         <f>(D10-C10)*((D9+C9)/2)</f>
         <v/>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="13">
         <f>(E10-D10)*((E9+D9)/2)</f>
         <v/>
       </c>
-      <c r="F37" s="19">
+      <c r="F37" s="13">
         <f>(F10-E10)*((F9+E9)/2)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Spread Effect on Change in ROE</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="13">
         <f>(D9-C9)*((D10+C10)/2)</f>
         <v/>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="13">
         <f>(E9-D9)*((E10+D10)/2)</f>
         <v/>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="13">
         <f>(F9-E9)*((F10+E10)/2)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Financing Effect on Change in ROE</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="13">
         <f>D37+D38</f>
         <v/>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="13">
         <f>E37+E38</f>
         <v/>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="13">
         <f>F37+F38</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Change in ROE from Drivers</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="13">
         <f>D36+D39</f>
         <v/>
       </c>
-      <c r="E40" s="19">
+      <c r="E40" s="13">
         <f>E36+E39</f>
         <v/>
       </c>
-      <c r="F40" s="19">
+      <c r="F40" s="13">
         <f>F36+F39</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>ROE CHANGE ATTRIBUTION CHECK</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="9">
         <f>IF(OR(ISNA(D40),ISNA(D35)),"N/A",IF(ABS(D40-D35)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="9">
         <f>IF(OR(ISNA(E40),ISNA(E35)),"N/A",IF(ABS(E40-E35)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="9">
         <f>IF(OR(ISNA(F40),ISNA(F35)),"N/A",IF(ABS(F40-F35)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
@@ -30192,103 +30159,103 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Accounting Judgment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>The supplied treatment is the model's reference treatment, not a universal accounting truth. Compare it with the listed alternative(s), choose the treatment you would defend, and explain the economic consequence.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Choose a treatment in column F only. That choice drives the matching Condensed Financials classification and downstream historical schedules; leaving F blank uses the supplied reference treatment. Columns D:E are display context and must not be edited. Enter your rationale and economic consequence in G:H. Formula Check grades formula cells against the treatment currently selected in F and validates that the generated classification links remain intact; it does not grade the judgment response itself. Do not edit the linked Condensed Financials classification cell directly.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Supplied reference treatment</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Alternative(s) to evaluate</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Treatment to defend</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Economic consequence</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Operating lease liabilities</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Lease liability operating vs financing</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Operating Long-Term Liability</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Financial Liability</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>Operating Long-Term Liability</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>The reference model keeps the liability in operating long-term liabilities under its current lease convention. Treating it as a financial liability is also defensible when the lease obligation is viewed as debt-like financing.</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>Operating-liability treatment lowers NOLA/NOA; financial-liability treatment raises Net Debt by the same balance. Implied equity is unchanged from this classification switch alone, but RNOA versus FLEV/Spread interpretation changes.</t>
         </is>
@@ -30324,103 +30291,103 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Normalization Judgment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>The supplied treatment is the model's reference convention, not a universal truth. Decide whether each supplied candidate should remain in recurring earnings or be normalized out.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Choose the treatment in column F. Blank F uses the supplied reference treatment. G:H are ungraded reasoning. Do not edit the generated Earnings Normalization treatment link directly.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Supplied reference treatment</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Alternative to evaluate</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Treatment to defend</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Economic consequence</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Restructuring expense</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>operating_pretax_effective_tax</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Non-recurring</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Recurring</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>Non-recurring</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>The reference model treats the supplied restructuring charge as non-recurring because the illustrative case identifies it as a discrete restructuring event rather than normal ongoing operations.</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>Non-recurring treatment removes the signed after-tax effect from normalized earnings; recurring treatment leaves reported earnings unchanged.</t>
         </is>
@@ -30455,14 +30422,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Earnings Normalization</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Reported statements stay unchanged. Bridge reported NOPAT / Net Income to normalized earnings using the treatments chosen on Normalization Judgment.</t>
         </is>
@@ -30470,276 +30437,276 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Treatment</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="10" t="n">
         <v>44561</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="10" t="n">
         <v>44926</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="10" t="n">
         <v>45291</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="10" t="n">
         <v>45657</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="10" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Restructuring expense</t>
         </is>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="9">
         <f>IF('Normalization Judgment'!$F$5="","Non-recurring",'Normalization Judgment'!$F$5)</f>
         <v/>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="11">
         <f>'Income Statement'!B11</f>
         <v/>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="11">
         <f>'Income Statement'!C11</f>
         <v/>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="11">
         <f>'Income Statement'!D11</f>
         <v/>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="11">
         <f>'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="11">
         <f>'Income Statement'!F11</f>
         <v/>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Reported NOPAT</t>
         </is>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="11">
         <f>'Condensed Financials'!B28</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="11">
         <f>'Condensed Financials'!C28</f>
         <v/>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="11">
         <f>'Condensed Financials'!D28</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="11">
         <f>'Condensed Financials'!E28</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="11">
         <f>'Condensed Financials'!F28</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Reported Net Income</t>
         </is>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="11">
         <f>'Condensed Financials'!B20</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="11">
         <f>'Condensed Financials'!C20</f>
         <v/>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="11">
         <f>'Condensed Financials'!D20</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="11">
         <f>'Condensed Financials'!E20</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="11">
         <f>'Condensed Financials'!F20</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Pretax Normalization Adjustment</t>
         </is>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="14">
         <f>-SUMIF($B$5:$B$5,"Non-recurring",C$5:C$5)</f>
         <v/>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="14">
         <f>-SUMIF($B$5:$B$5,"Non-recurring",D$5:D$5)</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="14">
         <f>-SUMIF($B$5:$B$5,"Non-recurring",E$5:E$5)</f>
         <v/>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="14">
         <f>-SUMIF($B$5:$B$5,"Non-recurring",F$5:F$5)</f>
         <v/>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="14">
         <f>-SUMIF($B$5:$B$5,"Non-recurring",G$5:G$5)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Effective Tax Rate</t>
         </is>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="17">
         <f>'Condensed Financials'!B25</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="17">
         <f>'Condensed Financials'!C25</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="17">
         <f>'Condensed Financials'!D25</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="17">
         <f>'Condensed Financials'!E25</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="17">
         <f>'Condensed Financials'!F25</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>After-tax Normalization Adjustment</t>
         </is>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="14">
         <f>IF(C9=0,0,IF(ISNA(C10),NA(),C9*(1-C10)))</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="14">
         <f>IF(D9=0,0,IF(ISNA(D10),NA(),D9*(1-D10)))</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="14">
         <f>IF(E9=0,0,IF(ISNA(E10),NA(),E9*(1-E10)))</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="14">
         <f>IF(F9=0,0,IF(ISNA(F10),NA(),F9*(1-F10)))</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="14">
         <f>IF(G9=0,0,IF(ISNA(G10),NA(),G9*(1-G10)))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Normalized NOPAT</t>
         </is>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="14">
         <f>C7+C11</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="14">
         <f>D7+D11</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="14">
         <f>E7+E11</f>
         <v/>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="14">
         <f>F7+F11</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="14">
         <f>G7+G11</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Normalized Net Income</t>
         </is>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="14">
         <f>C8+C11</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="14">
         <f>D8+D11</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="14">
         <f>E8+E11</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="14">
         <f>F8+F11</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="14">
         <f>G8+G11</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>NORMALIZATION CHECK</t>
         </is>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="9">
         <f>IF(AND(ABS((C12-C7)-C11)&lt;0.01,ABS((C13-C8)-C11)&lt;0.01),"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="9">
         <f>IF(AND(ABS((D12-D7)-D11)&lt;0.01,ABS((D13-D8)-D11)&lt;0.01),"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="9">
         <f>IF(AND(ABS((E12-E7)-E11)&lt;0.01,ABS((E13-E8)-E11)&lt;0.01),"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="9">
         <f>IF(AND(ABS((F12-F7)-F11)&lt;0.01,ABS((F13-F8)-F11)&lt;0.01),"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="9">
         <f>IF(AND(ABS((G12-G7)-G11)&lt;0.01,ABS((G13-G8)-G11)&lt;0.01),"OK","CHECK")</f>
         <v/>
       </c>

--- a/example/DEMO_HK_Answer_Key.xlsx
+++ b/example/DEMO_HK_Answer_Key.xlsx
@@ -1077,6 +1077,181 @@
         <t>Operating Effect plus Financing Effect.</t>
       </text>
     </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Link reported PP&amp;E for the same fiscal period.</t>
+      </text>
+    </comment>
+    <comment ref="C44" authorId="0" shapeId="0">
+      <text>
+        <t>Link reported PP&amp;E for the same fiscal period.</t>
+      </text>
+    </comment>
+    <comment ref="D44" authorId="0" shapeId="0">
+      <text>
+        <t>Link reported PP&amp;E for the same fiscal period.</t>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0">
+      <text>
+        <t>Link reported PP&amp;E for the same fiscal period.</t>
+      </text>
+    </comment>
+    <comment ref="F44" authorId="0" shapeId="0">
+      <text>
+        <t>Link reported PP&amp;E for the same fiscal period.</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>Link reported combined D&amp;A for the same fiscal period.</t>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="0" shapeId="0">
+      <text>
+        <t>Link reported combined D&amp;A for the same fiscal period.</t>
+      </text>
+    </comment>
+    <comment ref="D45" authorId="0" shapeId="0">
+      <text>
+        <t>Link reported combined D&amp;A for the same fiscal period.</t>
+      </text>
+    </comment>
+    <comment ref="E45" authorId="0" shapeId="0">
+      <text>
+        <t>Link reported combined D&amp;A for the same fiscal period.</t>
+      </text>
+    </comment>
+    <comment ref="F45" authorId="0" shapeId="0">
+      <text>
+        <t>Link reported combined D&amp;A for the same fiscal period.</t>
+      </text>
+    </comment>
+    <comment ref="C46" authorId="0" shapeId="0">
+      <text>
+        <t>Average beginning and ending PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="D46" authorId="0" shapeId="0">
+      <text>
+        <t>Average beginning and ending PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="E46" authorId="0" shapeId="0">
+      <text>
+        <t>Average beginning and ending PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="F46" authorId="0" shapeId="0">
+      <text>
+        <t>Average beginning and ending PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="C47" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue divided by Average PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="D47" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue divided by Average PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="E47" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue divided by Average PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="F47" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue divided by Average PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="C48" authorId="0" shapeId="0">
+      <text>
+        <t>Average PP&amp;E divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="D48" authorId="0" shapeId="0">
+      <text>
+        <t>Average PP&amp;E divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="E48" authorId="0" shapeId="0">
+      <text>
+        <t>Average PP&amp;E divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="F48" authorId="0" shapeId="0">
+      <text>
+        <t>Average PP&amp;E divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0">
+      <text>
+        <t>Current PP&amp;E minus prior PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="D49" authorId="0" shapeId="0">
+      <text>
+        <t>Current PP&amp;E minus prior PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="E49" authorId="0" shapeId="0">
+      <text>
+        <t>Current PP&amp;E minus prior PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="F49" authorId="0" shapeId="0">
+      <text>
+        <t>Current PP&amp;E minus prior PP&amp;E.</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Combined D&amp;A divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="0" shapeId="0">
+      <text>
+        <t>Combined D&amp;A divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="D50" authorId="0" shapeId="0">
+      <text>
+        <t>Combined D&amp;A divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="E50" authorId="0" shapeId="0">
+      <text>
+        <t>Combined D&amp;A divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="F50" authorId="0" shapeId="0">
+      <text>
+        <t>Combined D&amp;A divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="C51" authorId="0" shapeId="0">
+      <text>
+        <t>Combined D&amp;A divided by Average PP&amp;E (context ratio only).</t>
+      </text>
+    </comment>
+    <comment ref="D51" authorId="0" shapeId="0">
+      <text>
+        <t>Combined D&amp;A divided by Average PP&amp;E (context ratio only).</t>
+      </text>
+    </comment>
+    <comment ref="E51" authorId="0" shapeId="0">
+      <text>
+        <t>Combined D&amp;A divided by Average PP&amp;E (context ratio only).</t>
+      </text>
+    </comment>
+    <comment ref="F51" authorId="0" shapeId="0">
+      <text>
+        <t>Combined D&amp;A divided by Average PP&amp;E (context ratio only).</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1925,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3960,6 +4135,246 @@
       <c r="F70" s="9" t="inlineStr">
         <is>
           <t>accrual_ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Property, Plant &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>B44:F44</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortisation</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>B45:F45</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>C46:F46</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>ppe_source_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>PP&amp;E Turnover</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>C47:F47</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>revenue_link, average_ppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>PP&amp;E Intensity</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>C48:F48</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>revenue_link, average_ppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>Change in PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>C49:F49</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>ppe_source_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>B50:F50</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>da_source_link, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>D&amp;A / Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>C51:F51</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>da_source_link, average_ppe</t>
         </is>
       </c>
     </row>
@@ -4966,7 +5381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S280"/>
+  <dimension ref="A1:S315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27225,6 +27640,2791 @@
         <v>4</v>
       </c>
       <c r="S280" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20211231</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>280</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Property, Plant &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Link reported PP&amp;E for the same fiscal period.</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe.2021-12-31</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>B44</t>
+        </is>
+      </c>
+      <c r="I281">
+        <f>'Balance Sheet'!B10</f>
+        <v/>
+      </c>
+      <c r="J281" t="n">
+        <v>3200</v>
+      </c>
+      <c r="K281" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Pull ending Property, Plant &amp; Equipment for the same fiscal period.|This is a source link, not an investment conclusion.</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>ppe_source_link</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>79</v>
+      </c>
+      <c r="R281" t="n">
+        <v>0</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20221231</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>281</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Property, Plant &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Link reported PP&amp;E for the same fiscal period.</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>C44</t>
+        </is>
+      </c>
+      <c r="I282">
+        <f>'Balance Sheet'!C10</f>
+        <v/>
+      </c>
+      <c r="J282" t="n">
+        <v>3400</v>
+      </c>
+      <c r="K282" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Pull ending Property, Plant &amp; Equipment for the same fiscal period.|This is a source link, not an investment conclusion.</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>ppe_source_link</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>79</v>
+      </c>
+      <c r="R282" t="n">
+        <v>1</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20231231</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>282</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Property, Plant &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Link reported PP&amp;E for the same fiscal period.</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D44</t>
+        </is>
+      </c>
+      <c r="I283">
+        <f>'Balance Sheet'!D10</f>
+        <v/>
+      </c>
+      <c r="J283" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K283" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Pull ending Property, Plant &amp; Equipment for the same fiscal period.|This is a source link, not an investment conclusion.</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>ppe_source_link</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>79</v>
+      </c>
+      <c r="R283" t="n">
+        <v>2</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20241231</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>283</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Property, Plant &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Link reported PP&amp;E for the same fiscal period.</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>E44</t>
+        </is>
+      </c>
+      <c r="I284">
+        <f>'Balance Sheet'!E10</f>
+        <v/>
+      </c>
+      <c r="J284" t="n">
+        <v>3800</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Pull ending Property, Plant &amp; Equipment for the same fiscal period.|This is a source link, not an investment conclusion.</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>ppe_source_link</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>79</v>
+      </c>
+      <c r="R284" t="n">
+        <v>3</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20251231</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>284</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Property, Plant &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Link reported PP&amp;E for the same fiscal period.</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>F44</t>
+        </is>
+      </c>
+      <c r="I285">
+        <f>'Balance Sheet'!F10</f>
+        <v/>
+      </c>
+      <c r="J285" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Pull ending Property, Plant &amp; Equipment for the same fiscal period.|This is a source link, not an investment conclusion.</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>ppe_source_link</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>79</v>
+      </c>
+      <c r="R285" t="n">
+        <v>4</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>da_source_link__20211231</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>285</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortisation</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Link reported combined D&amp;A for the same fiscal period.</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>fixed_asset.depreciation_amortization.2021-12-31</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>B45</t>
+        </is>
+      </c>
+      <c r="I286">
+        <f>'Cash Flow Statement'!B8</f>
+        <v/>
+      </c>
+      <c r="J286" t="n">
+        <v>340</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Pull Depreciation &amp; Amortisation for the same fiscal period.|Combined D&amp;A may include intangible amortisation; do not treat it as a pure PP&amp;E depreciation charge.</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>da_source_link</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>80</v>
+      </c>
+      <c r="R286" t="n">
+        <v>0</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>da_source_link__20221231</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>286</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortisation</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Link reported combined D&amp;A for the same fiscal period.</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>fixed_asset.depreciation_amortization.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>C45</t>
+        </is>
+      </c>
+      <c r="I287">
+        <f>'Cash Flow Statement'!C8</f>
+        <v/>
+      </c>
+      <c r="J287" t="n">
+        <v>368</v>
+      </c>
+      <c r="K287" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Pull Depreciation &amp; Amortisation for the same fiscal period.|Combined D&amp;A may include intangible amortisation; do not treat it as a pure PP&amp;E depreciation charge.</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>da_source_link</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>80</v>
+      </c>
+      <c r="R287" t="n">
+        <v>1</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>da_source_link__20231231</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>287</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortisation</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Link reported combined D&amp;A for the same fiscal period.</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>fixed_asset.depreciation_amortization.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D45</t>
+        </is>
+      </c>
+      <c r="I288">
+        <f>'Cash Flow Statement'!D8</f>
+        <v/>
+      </c>
+      <c r="J288" t="n">
+        <v>404</v>
+      </c>
+      <c r="K288" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Pull Depreciation &amp; Amortisation for the same fiscal period.|Combined D&amp;A may include intangible amortisation; do not treat it as a pure PP&amp;E depreciation charge.</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>da_source_link</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>80</v>
+      </c>
+      <c r="R288" t="n">
+        <v>2</v>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>da_source_link__20241231</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>288</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortisation</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Link reported combined D&amp;A for the same fiscal period.</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>fixed_asset.depreciation_amortization.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>E45</t>
+        </is>
+      </c>
+      <c r="I289">
+        <f>'Cash Flow Statement'!E8</f>
+        <v/>
+      </c>
+      <c r="J289" t="n">
+        <v>448</v>
+      </c>
+      <c r="K289" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Pull Depreciation &amp; Amortisation for the same fiscal period.|Combined D&amp;A may include intangible amortisation; do not treat it as a pure PP&amp;E depreciation charge.</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>da_source_link</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>80</v>
+      </c>
+      <c r="R289" t="n">
+        <v>3</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>da_source_link__20251231</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>289</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortisation</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Link reported combined D&amp;A for the same fiscal period.</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>fixed_asset.depreciation_amortization.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>F45</t>
+        </is>
+      </c>
+      <c r="I290">
+        <f>'Cash Flow Statement'!F8</f>
+        <v/>
+      </c>
+      <c r="J290" t="n">
+        <v>500</v>
+      </c>
+      <c r="K290" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Pull Depreciation &amp; Amortisation for the same fiscal period.|Combined D&amp;A may include intangible amortisation; do not treat it as a pure PP&amp;E depreciation charge.</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>da_source_link</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>80</v>
+      </c>
+      <c r="R290" t="n">
+        <v>4</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>average_ppe__20221231</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>290</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Average beginning and ending PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>fixed_asset.average_ppe.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>C46</t>
+        </is>
+      </c>
+      <c r="I291">
+        <f>(B44+C44)/2</f>
+        <v/>
+      </c>
+      <c r="J291" t="n">
+        <v>3300</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20221231,ppe_source_link__20211231</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E = (Prior PP&amp;E + Current PP&amp;E) / 2.</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>average_ppe</t>
+        </is>
+      </c>
+      <c r="Q291" t="n">
+        <v>81</v>
+      </c>
+      <c r="R291" t="n">
+        <v>1</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>average_ppe__20231231</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>291</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Average beginning and ending PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>fixed_asset.average_ppe.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>D46</t>
+        </is>
+      </c>
+      <c r="I292">
+        <f>(C44+D44)/2</f>
+        <v/>
+      </c>
+      <c r="J292" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K292" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20231231,ppe_source_link__20221231</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E = (Prior PP&amp;E + Current PP&amp;E) / 2.</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>average_ppe</t>
+        </is>
+      </c>
+      <c r="Q292" t="n">
+        <v>81</v>
+      </c>
+      <c r="R292" t="n">
+        <v>2</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>average_ppe__20241231</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>292</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Average beginning and ending PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>fixed_asset.average_ppe.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>E46</t>
+        </is>
+      </c>
+      <c r="I293">
+        <f>(D44+E44)/2</f>
+        <v/>
+      </c>
+      <c r="J293" t="n">
+        <v>3700</v>
+      </c>
+      <c r="K293" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20241231,ppe_source_link__20231231</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E = (Prior PP&amp;E + Current PP&amp;E) / 2.</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>average_ppe</t>
+        </is>
+      </c>
+      <c r="Q293" t="n">
+        <v>81</v>
+      </c>
+      <c r="R293" t="n">
+        <v>3</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>average_ppe__20251231</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>293</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Average beginning and ending PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>fixed_asset.average_ppe.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>F46</t>
+        </is>
+      </c>
+      <c r="I294">
+        <f>(E44+F44)/2</f>
+        <v/>
+      </c>
+      <c r="J294" t="n">
+        <v>3900</v>
+      </c>
+      <c r="K294" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20251231,ppe_source_link__20241231</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E = (Prior PP&amp;E + Current PP&amp;E) / 2.</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>average_ppe</t>
+        </is>
+      </c>
+      <c r="Q294" t="n">
+        <v>81</v>
+      </c>
+      <c r="R294" t="n">
+        <v>4</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ppe_turnover__20221231</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>294</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>PP&amp;E Turnover</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Revenue divided by Average PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_turnover.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>C47</t>
+        </is>
+      </c>
+      <c r="I295">
+        <f>IF(C46=0,NA(),'Condensed Financials'!C19/C46)</f>
+        <v/>
+      </c>
+      <c r="J295" t="n">
+        <v>2.787878787878788</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>revenue_link__20221231,average_ppe__20221231</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>PP&amp;E Turnover = Revenue / Average PP&amp;E.|A zero Average PP&amp;E denominator makes the ratio undefined (#N/A).|The ratio alone does not imply under- or over-investment.</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>ppe_turnover</t>
+        </is>
+      </c>
+      <c r="Q295" t="n">
+        <v>82</v>
+      </c>
+      <c r="R295" t="n">
+        <v>1</v>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ppe_turnover__20231231</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>295</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>PP&amp;E Turnover</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Revenue divided by Average PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_turnover.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+      <c r="I296">
+        <f>IF(D46=0,NA(),'Condensed Financials'!D19/D46)</f>
+        <v/>
+      </c>
+      <c r="J296" t="n">
+        <v>2.885714285714286</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>revenue_link__20231231,average_ppe__20231231</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>PP&amp;E Turnover = Revenue / Average PP&amp;E.|A zero Average PP&amp;E denominator makes the ratio undefined (#N/A).|The ratio alone does not imply under- or over-investment.</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>ppe_turnover</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>82</v>
+      </c>
+      <c r="R296" t="n">
+        <v>2</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ppe_turnover__20241231</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>296</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>PP&amp;E Turnover</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Revenue divided by Average PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_turnover.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>E47</t>
+        </is>
+      </c>
+      <c r="I297">
+        <f>IF(E46=0,NA(),'Condensed Financials'!E19/E46)</f>
+        <v/>
+      </c>
+      <c r="J297" t="n">
+        <v>3.027027027027027</v>
+      </c>
+      <c r="K297" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>revenue_link__20241231,average_ppe__20241231</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>PP&amp;E Turnover = Revenue / Average PP&amp;E.|A zero Average PP&amp;E denominator makes the ratio undefined (#N/A).|The ratio alone does not imply under- or over-investment.</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>ppe_turnover</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>82</v>
+      </c>
+      <c r="R297" t="n">
+        <v>3</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ppe_turnover__20251231</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>297</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>PP&amp;E Turnover</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Revenue divided by Average PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_turnover.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>F47</t>
+        </is>
+      </c>
+      <c r="I298">
+        <f>IF(F46=0,NA(),'Condensed Financials'!F19/F46)</f>
+        <v/>
+      </c>
+      <c r="J298" t="n">
+        <v>3.205128205128205</v>
+      </c>
+      <c r="K298" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>revenue_link__20251231,average_ppe__20251231</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>PP&amp;E Turnover = Revenue / Average PP&amp;E.|A zero Average PP&amp;E denominator makes the ratio undefined (#N/A).|The ratio alone does not imply under- or over-investment.</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>ppe_turnover</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>82</v>
+      </c>
+      <c r="R298" t="n">
+        <v>4</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ppe_intensity__20221231</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>298</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>PP&amp;E Intensity</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_intensity.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>C48</t>
+        </is>
+      </c>
+      <c r="I299">
+        <f>IF('Condensed Financials'!C19=0,NA(),C46/'Condensed Financials'!C19)</f>
+        <v/>
+      </c>
+      <c r="J299" t="n">
+        <v>0.358695652173913</v>
+      </c>
+      <c r="K299" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>revenue_link__20221231,average_ppe__20221231</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>PP&amp;E Intensity = Average PP&amp;E / Revenue.|When defined, PP&amp;E Turnover × PP&amp;E Intensity = 1.|A higher intensity is not automatically bad; diagnose the asset mix first.</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>ppe_intensity</t>
+        </is>
+      </c>
+      <c r="Q299" t="n">
+        <v>83</v>
+      </c>
+      <c r="R299" t="n">
+        <v>1</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ppe_intensity__20231231</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>299</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>PP&amp;E Intensity</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_intensity.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>D48</t>
+        </is>
+      </c>
+      <c r="I300">
+        <f>IF('Condensed Financials'!D19=0,NA(),D46/'Condensed Financials'!D19)</f>
+        <v/>
+      </c>
+      <c r="J300" t="n">
+        <v>0.3465346534653465</v>
+      </c>
+      <c r="K300" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>revenue_link__20231231,average_ppe__20231231</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>PP&amp;E Intensity = Average PP&amp;E / Revenue.|When defined, PP&amp;E Turnover × PP&amp;E Intensity = 1.|A higher intensity is not automatically bad; diagnose the asset mix first.</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>ppe_intensity</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>83</v>
+      </c>
+      <c r="R300" t="n">
+        <v>2</v>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ppe_intensity__20241231</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>300</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>PP&amp;E Intensity</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_intensity.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>E48</t>
+        </is>
+      </c>
+      <c r="I301">
+        <f>IF('Condensed Financials'!E19=0,NA(),E46/'Condensed Financials'!E19)</f>
+        <v/>
+      </c>
+      <c r="J301" t="n">
+        <v>0.3303571428571428</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>revenue_link__20241231,average_ppe__20241231</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>PP&amp;E Intensity = Average PP&amp;E / Revenue.|When defined, PP&amp;E Turnover × PP&amp;E Intensity = 1.|A higher intensity is not automatically bad; diagnose the asset mix first.</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>ppe_intensity</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>83</v>
+      </c>
+      <c r="R301" t="n">
+        <v>3</v>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ppe_intensity__20251231</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>301</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>PP&amp;E Intensity</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_intensity.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>F48</t>
+        </is>
+      </c>
+      <c r="I302">
+        <f>IF('Condensed Financials'!F19=0,NA(),F46/'Condensed Financials'!F19)</f>
+        <v/>
+      </c>
+      <c r="J302" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>revenue_link__20251231,average_ppe__20251231</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>PP&amp;E Intensity = Average PP&amp;E / Revenue.|When defined, PP&amp;E Turnover × PP&amp;E Intensity = 1.|A higher intensity is not automatically bad; diagnose the asset mix first.</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>ppe_intensity</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>83</v>
+      </c>
+      <c r="R302" t="n">
+        <v>4</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ppe_change__20221231</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>302</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Change in PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Current PP&amp;E minus prior PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_change.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>C49</t>
+        </is>
+      </c>
+      <c r="I303">
+        <f>C44-B44</f>
+        <v/>
+      </c>
+      <c r="J303" t="n">
+        <v>200</v>
+      </c>
+      <c r="K303" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20221231,ppe_source_link__20211231</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Change in PP&amp;E = Current PP&amp;E − Prior PP&amp;E.|This is not a capex amount; do not infer purchases of PP&amp;E from the change alone.</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>ppe_change</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>84</v>
+      </c>
+      <c r="R303" t="n">
+        <v>1</v>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ppe_change__20231231</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>303</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Change in PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Current PP&amp;E minus prior PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_change.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>D49</t>
+        </is>
+      </c>
+      <c r="I304">
+        <f>D44-C44</f>
+        <v/>
+      </c>
+      <c r="J304" t="n">
+        <v>200</v>
+      </c>
+      <c r="K304" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20231231,ppe_source_link__20221231</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Change in PP&amp;E = Current PP&amp;E − Prior PP&amp;E.|This is not a capex amount; do not infer purchases of PP&amp;E from the change alone.</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>ppe_change</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>84</v>
+      </c>
+      <c r="R304" t="n">
+        <v>2</v>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ppe_change__20241231</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>304</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Change in PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Current PP&amp;E minus prior PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_change.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>E49</t>
+        </is>
+      </c>
+      <c r="I305">
+        <f>E44-D44</f>
+        <v/>
+      </c>
+      <c r="J305" t="n">
+        <v>200</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20241231,ppe_source_link__20231231</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Change in PP&amp;E = Current PP&amp;E − Prior PP&amp;E.|This is not a capex amount; do not infer purchases of PP&amp;E from the change alone.</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>ppe_change</t>
+        </is>
+      </c>
+      <c r="Q305" t="n">
+        <v>84</v>
+      </c>
+      <c r="R305" t="n">
+        <v>3</v>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ppe_change__20251231</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>305</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Change in PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Current PP&amp;E minus prior PP&amp;E.</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>fixed_asset.ppe_change.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>F49</t>
+        </is>
+      </c>
+      <c r="I306">
+        <f>F44-E44</f>
+        <v/>
+      </c>
+      <c r="J306" t="n">
+        <v>200</v>
+      </c>
+      <c r="K306" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>ppe_source_link__20251231,ppe_source_link__20241231</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Change in PP&amp;E = Current PP&amp;E − Prior PP&amp;E.|This is not a capex amount; do not infer purchases of PP&amp;E from the change alone.</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>ppe_change</t>
+        </is>
+      </c>
+      <c r="Q306" t="n">
+        <v>84</v>
+      </c>
+      <c r="R306" t="n">
+        <v>4</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>da_to_revenue__20211231</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>306</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Combined D&amp;A divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>fixed_asset.da_to_revenue.2021-12-31</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>B50</t>
+        </is>
+      </c>
+      <c r="I307">
+        <f>IF('Condensed Financials'!B19=0,NA(),B45/'Condensed Financials'!B19)</f>
+        <v/>
+      </c>
+      <c r="J307" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K307" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>da_source_link__20211231,revenue_link__20211231</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue = Depreciation &amp; Amortisation / Revenue.|A zero Revenue denominator makes the ratio undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>da_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q307" t="n">
+        <v>85</v>
+      </c>
+      <c r="R307" t="n">
+        <v>0</v>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>da_to_revenue__20221231</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>307</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Combined D&amp;A divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>fixed_asset.da_to_revenue.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>C50</t>
+        </is>
+      </c>
+      <c r="I308">
+        <f>IF('Condensed Financials'!C19=0,NA(),C45/'Condensed Financials'!C19)</f>
+        <v/>
+      </c>
+      <c r="J308" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K308" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>da_source_link__20221231,revenue_link__20221231</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue = Depreciation &amp; Amortisation / Revenue.|A zero Revenue denominator makes the ratio undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>da_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>85</v>
+      </c>
+      <c r="R308" t="n">
+        <v>1</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>da_to_revenue__20231231</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>308</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Combined D&amp;A divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>fixed_asset.da_to_revenue.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>D50</t>
+        </is>
+      </c>
+      <c r="I309">
+        <f>IF('Condensed Financials'!D19=0,NA(),D45/'Condensed Financials'!D19)</f>
+        <v/>
+      </c>
+      <c r="J309" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K309" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>da_source_link__20231231,revenue_link__20231231</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue = Depreciation &amp; Amortisation / Revenue.|A zero Revenue denominator makes the ratio undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>da_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q309" t="n">
+        <v>85</v>
+      </c>
+      <c r="R309" t="n">
+        <v>2</v>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>da_to_revenue__20241231</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>309</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Combined D&amp;A divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>fixed_asset.da_to_revenue.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>E50</t>
+        </is>
+      </c>
+      <c r="I310">
+        <f>IF('Condensed Financials'!E19=0,NA(),E45/'Condensed Financials'!E19)</f>
+        <v/>
+      </c>
+      <c r="J310" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K310" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>da_source_link__20241231,revenue_link__20241231</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue = Depreciation &amp; Amortisation / Revenue.|A zero Revenue denominator makes the ratio undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>da_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q310" t="n">
+        <v>85</v>
+      </c>
+      <c r="R310" t="n">
+        <v>3</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>da_to_revenue__20251231</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>310</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Combined D&amp;A divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>fixed_asset.da_to_revenue.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>F50</t>
+        </is>
+      </c>
+      <c r="I311">
+        <f>IF('Condensed Financials'!F19=0,NA(),F45/'Condensed Financials'!F19)</f>
+        <v/>
+      </c>
+      <c r="J311" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K311" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>da_source_link__20251231,revenue_link__20251231</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue = Depreciation &amp; Amortisation / Revenue.|A zero Revenue denominator makes the ratio undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>da_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q311" t="n">
+        <v>85</v>
+      </c>
+      <c r="R311" t="n">
+        <v>4</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>da_to_average_ppe__20221231</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>311</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>D&amp;A / Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Combined D&amp;A divided by Average PP&amp;E (context ratio only).</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>fixed_asset.da_to_average_ppe.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>C51</t>
+        </is>
+      </c>
+      <c r="I312">
+        <f>IF(C46=0,NA(),C45/C46)</f>
+        <v/>
+      </c>
+      <c r="J312" t="n">
+        <v>0.1115151515151515</v>
+      </c>
+      <c r="K312" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>da_source_link__20221231,average_ppe__20221231</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>D&amp;A / Average PP&amp;E = Depreciation &amp; Amortisation / Average PP&amp;E.|This is a context ratio, not automatically a pure PP&amp;E depreciation rate, because the supplied D&amp;A line may include intangible amortisation.|Do not treat the ratio as a good/bad investment conclusion by itself.</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>da_to_average_ppe</t>
+        </is>
+      </c>
+      <c r="Q312" t="n">
+        <v>86</v>
+      </c>
+      <c r="R312" t="n">
+        <v>1</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>da_to_average_ppe__20231231</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>312</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>D&amp;A / Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Combined D&amp;A divided by Average PP&amp;E (context ratio only).</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>fixed_asset.da_to_average_ppe.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>D51</t>
+        </is>
+      </c>
+      <c r="I313">
+        <f>IF(D46=0,NA(),D45/D46)</f>
+        <v/>
+      </c>
+      <c r="J313" t="n">
+        <v>0.1154285714285714</v>
+      </c>
+      <c r="K313" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>da_source_link__20231231,average_ppe__20231231</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>D&amp;A / Average PP&amp;E = Depreciation &amp; Amortisation / Average PP&amp;E.|This is a context ratio, not automatically a pure PP&amp;E depreciation rate, because the supplied D&amp;A line may include intangible amortisation.|Do not treat the ratio as a good/bad investment conclusion by itself.</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>da_to_average_ppe</t>
+        </is>
+      </c>
+      <c r="Q313" t="n">
+        <v>86</v>
+      </c>
+      <c r="R313" t="n">
+        <v>2</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>da_to_average_ppe__20241231</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>313</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>D&amp;A / Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Combined D&amp;A divided by Average PP&amp;E (context ratio only).</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>fixed_asset.da_to_average_ppe.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>E51</t>
+        </is>
+      </c>
+      <c r="I314">
+        <f>IF(E46=0,NA(),E45/E46)</f>
+        <v/>
+      </c>
+      <c r="J314" t="n">
+        <v>0.1210810810810811</v>
+      </c>
+      <c r="K314" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>da_source_link__20241231,average_ppe__20241231</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>D&amp;A / Average PP&amp;E = Depreciation &amp; Amortisation / Average PP&amp;E.|This is a context ratio, not automatically a pure PP&amp;E depreciation rate, because the supplied D&amp;A line may include intangible amortisation.|Do not treat the ratio as a good/bad investment conclusion by itself.</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>da_to_average_ppe</t>
+        </is>
+      </c>
+      <c r="Q314" t="n">
+        <v>86</v>
+      </c>
+      <c r="R314" t="n">
+        <v>3</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>da_to_average_ppe__20251231</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>314</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>D&amp;A / Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Combined D&amp;A divided by Average PP&amp;E (context ratio only).</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>fixed_asset.da_to_average_ppe.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>fixed_asset</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>F51</t>
+        </is>
+      </c>
+      <c r="I315">
+        <f>IF(F46=0,NA(),F45/F46)</f>
+        <v/>
+      </c>
+      <c r="J315" t="n">
+        <v>0.1282051282051282</v>
+      </c>
+      <c r="K315" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>da_source_link__20251231,average_ppe__20251231</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>D&amp;A / Average PP&amp;E = Depreciation &amp; Amortisation / Average PP&amp;E.|This is a context ratio, not automatically a pure PP&amp;E depreciation rate, because the supplied D&amp;A line may include intangible amortisation.|Do not treat the ratio as a good/bad investment conclusion by itself.</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>da_to_average_ppe</t>
+        </is>
+      </c>
+      <c r="Q315" t="n">
+        <v>86</v>
+      </c>
+      <c r="R315" t="n">
+        <v>4</v>
+      </c>
+      <c r="S315" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
@@ -29228,7 +32428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -30130,6 +33330,263 @@
       </c>
       <c r="F41" s="9">
         <f>IF(OR(ISNA(F40),ISNA(F35)),"N/A",IF(ABS(F40-F35)&lt;0.0000001,"OK","CHECK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>FIXED-ASSET INTENSITY CONTEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Property, Plant &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B44" s="14">
+        <f>'Balance Sheet'!B10</f>
+        <v/>
+      </c>
+      <c r="C44" s="14">
+        <f>'Balance Sheet'!C10</f>
+        <v/>
+      </c>
+      <c r="D44" s="14">
+        <f>'Balance Sheet'!D10</f>
+        <v/>
+      </c>
+      <c r="E44" s="14">
+        <f>'Balance Sheet'!E10</f>
+        <v/>
+      </c>
+      <c r="F44" s="14">
+        <f>'Balance Sheet'!F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortisation</t>
+        </is>
+      </c>
+      <c r="B45" s="14">
+        <f>'Cash Flow Statement'!B8</f>
+        <v/>
+      </c>
+      <c r="C45" s="14">
+        <f>'Cash Flow Statement'!C8</f>
+        <v/>
+      </c>
+      <c r="D45" s="14">
+        <f>'Cash Flow Statement'!D8</f>
+        <v/>
+      </c>
+      <c r="E45" s="14">
+        <f>'Cash Flow Statement'!E8</f>
+        <v/>
+      </c>
+      <c r="F45" s="14">
+        <f>'Cash Flow Statement'!F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="14">
+        <f>(B44+C44)/2</f>
+        <v/>
+      </c>
+      <c r="D46" s="14">
+        <f>(C44+D44)/2</f>
+        <v/>
+      </c>
+      <c r="E46" s="14">
+        <f>(D44+E44)/2</f>
+        <v/>
+      </c>
+      <c r="F46" s="14">
+        <f>(E44+F44)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>PP&amp;E Turnover</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="15">
+        <f>IF(C46=0,NA(),'Condensed Financials'!C19/C46)</f>
+        <v/>
+      </c>
+      <c r="D47" s="15">
+        <f>IF(D46=0,NA(),'Condensed Financials'!D19/D46)</f>
+        <v/>
+      </c>
+      <c r="E47" s="15">
+        <f>IF(E46=0,NA(),'Condensed Financials'!E19/E46)</f>
+        <v/>
+      </c>
+      <c r="F47" s="15">
+        <f>IF(F46=0,NA(),'Condensed Financials'!F19/F46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>PP&amp;E Intensity</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="13">
+        <f>IF('Condensed Financials'!C19=0,NA(),C46/'Condensed Financials'!C19)</f>
+        <v/>
+      </c>
+      <c r="D48" s="13">
+        <f>IF('Condensed Financials'!D19=0,NA(),D46/'Condensed Financials'!D19)</f>
+        <v/>
+      </c>
+      <c r="E48" s="13">
+        <f>IF('Condensed Financials'!E19=0,NA(),E46/'Condensed Financials'!E19)</f>
+        <v/>
+      </c>
+      <c r="F48" s="13">
+        <f>IF('Condensed Financials'!F19=0,NA(),F46/'Condensed Financials'!F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Change in PP&amp;E</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="14">
+        <f>C44-B44</f>
+        <v/>
+      </c>
+      <c r="D49" s="14">
+        <f>D44-C44</f>
+        <v/>
+      </c>
+      <c r="E49" s="14">
+        <f>E44-D44</f>
+        <v/>
+      </c>
+      <c r="F49" s="14">
+        <f>F44-E44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>D&amp;A / Revenue</t>
+        </is>
+      </c>
+      <c r="B50" s="13">
+        <f>IF('Condensed Financials'!B19=0,NA(),B45/'Condensed Financials'!B19)</f>
+        <v/>
+      </c>
+      <c r="C50" s="13">
+        <f>IF('Condensed Financials'!C19=0,NA(),C45/'Condensed Financials'!C19)</f>
+        <v/>
+      </c>
+      <c r="D50" s="13">
+        <f>IF('Condensed Financials'!D19=0,NA(),D45/'Condensed Financials'!D19)</f>
+        <v/>
+      </c>
+      <c r="E50" s="13">
+        <f>IF('Condensed Financials'!E19=0,NA(),E45/'Condensed Financials'!E19)</f>
+        <v/>
+      </c>
+      <c r="F50" s="13">
+        <f>IF('Condensed Financials'!F19=0,NA(),F45/'Condensed Financials'!F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>D&amp;A / Average PP&amp;E</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" s="13">
+        <f>IF(C46=0,NA(),C45/C46)</f>
+        <v/>
+      </c>
+      <c r="D51" s="13">
+        <f>IF(D46=0,NA(),D45/D46)</f>
+        <v/>
+      </c>
+      <c r="E51" s="13">
+        <f>IF(E46=0,NA(),E45/E46)</f>
+        <v/>
+      </c>
+      <c r="F51" s="13">
+        <f>IF(F46=0,NA(),F45/F46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>FIXED-ASSET INTENSITY CHECK</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" s="9">
+        <f>IF(OR(ISNA(C47),ISNA(C48)),"N/A",IF(ABS(C47*C48-1)&lt;0.0000001,"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="D52" s="9">
+        <f>IF(OR(ISNA(D47),ISNA(D48)),"N/A",IF(ABS(D47*D48-1)&lt;0.0000001,"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="E52" s="9">
+        <f>IF(OR(ISNA(E47),ISNA(E48)),"N/A",IF(ABS(E47*E48-1)&lt;0.0000001,"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="F52" s="9">
+        <f>IF(OR(ISNA(F47),ISNA(F48)),"N/A",IF(ABS(F47*F48-1)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
     </row>

--- a/example/DEMO_HK_Answer_Key.xlsx
+++ b/example/DEMO_HK_Answer_Key.xlsx
@@ -1252,6 +1252,96 @@
         <t>Combined D&amp;A divided by Average PP&amp;E (context ratio only).</t>
       </text>
     </comment>
+    <comment ref="B55" authorId="0" shapeId="0">
+      <text>
+        <t>Link the reported aggregate lease-liability balance.</t>
+      </text>
+    </comment>
+    <comment ref="C55" authorId="0" shapeId="0">
+      <text>
+        <t>Link the reported aggregate lease-liability balance.</t>
+      </text>
+    </comment>
+    <comment ref="D55" authorId="0" shapeId="0">
+      <text>
+        <t>Link the reported aggregate lease-liability balance.</t>
+      </text>
+    </comment>
+    <comment ref="E55" authorId="0" shapeId="0">
+      <text>
+        <t>Link the reported aggregate lease-liability balance.</t>
+      </text>
+    </comment>
+    <comment ref="F55" authorId="0" shapeId="0">
+      <text>
+        <t>Link the reported aggregate lease-liability balance.</t>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0" shapeId="0">
+      <text>
+        <t>Reported lease liability divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="C56" authorId="0" shapeId="0">
+      <text>
+        <t>Reported lease liability divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="D56" authorId="0" shapeId="0">
+      <text>
+        <t>Reported lease liability divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="E56" authorId="0" shapeId="0">
+      <text>
+        <t>Reported lease liability divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="F56" authorId="0" shapeId="0">
+      <text>
+        <t>Reported lease liability divided by Revenue.</t>
+      </text>
+    </comment>
+    <comment ref="C57" authorId="0" shapeId="0">
+      <text>
+        <t>Current lease liability minus prior lease liability.</t>
+      </text>
+    </comment>
+    <comment ref="D57" authorId="0" shapeId="0">
+      <text>
+        <t>Current lease liability minus prior lease liability.</t>
+      </text>
+    </comment>
+    <comment ref="E57" authorId="0" shapeId="0">
+      <text>
+        <t>Current lease liability minus prior lease liability.</t>
+      </text>
+    </comment>
+    <comment ref="F57" authorId="0" shapeId="0">
+      <text>
+        <t>Current lease liability minus prior lease liability.</t>
+      </text>
+    </comment>
+    <comment ref="C58" authorId="0" shapeId="0">
+      <text>
+        <t>Percentage change in reported lease liability.</t>
+      </text>
+    </comment>
+    <comment ref="D58" authorId="0" shapeId="0">
+      <text>
+        <t>Percentage change in reported lease liability.</t>
+      </text>
+    </comment>
+    <comment ref="E58" authorId="0" shapeId="0">
+      <text>
+        <t>Percentage change in reported lease liability.</t>
+      </text>
+    </comment>
+    <comment ref="F58" authorId="0" shapeId="0">
+      <text>
+        <t>Percentage change in reported lease liability.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -2100,7 +2190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4375,6 +4465,126 @@
       <c r="F78" s="9" t="inlineStr">
         <is>
           <t>da_source_link, average_ppe</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>Lease Liability</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>B55:F55</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>B56:F56</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>Change in Lease Liability</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>C57:F57</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>Lease Liability Growth</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>C58:F58</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S315"/>
+  <dimension ref="A1:S333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30425,6 +30635,1439 @@
         <v>4</v>
       </c>
       <c r="S315" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20211231</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>315</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Lease Liability</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Link the reported aggregate lease-liability balance.</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability.2021-12-31</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>B55</t>
+        </is>
+      </c>
+      <c r="I316">
+        <f>'Balance Sheet'!B16</f>
+        <v/>
+      </c>
+      <c r="J316" t="n">
+        <v>300</v>
+      </c>
+      <c r="K316" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Pull the reported aggregate lease-liability balance for the same fiscal period.|Classification as operating vs financial liability is a separate Accounting Judgment.|This is not an ROU asset, lease payment, commitment, or amortization schedule.</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link</t>
+        </is>
+      </c>
+      <c r="Q316" t="n">
+        <v>87</v>
+      </c>
+      <c r="R316" t="n">
+        <v>0</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20221231</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>316</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Lease Liability</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Link the reported aggregate lease-liability balance.</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>C55</t>
+        </is>
+      </c>
+      <c r="I317">
+        <f>'Balance Sheet'!C16</f>
+        <v/>
+      </c>
+      <c r="J317" t="n">
+        <v>320</v>
+      </c>
+      <c r="K317" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Pull the reported aggregate lease-liability balance for the same fiscal period.|Classification as operating vs financial liability is a separate Accounting Judgment.|This is not an ROU asset, lease payment, commitment, or amortization schedule.</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link</t>
+        </is>
+      </c>
+      <c r="Q317" t="n">
+        <v>87</v>
+      </c>
+      <c r="R317" t="n">
+        <v>1</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20231231</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>317</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Lease Liability</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Link the reported aggregate lease-liability balance.</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>D55</t>
+        </is>
+      </c>
+      <c r="I318">
+        <f>'Balance Sheet'!D16</f>
+        <v/>
+      </c>
+      <c r="J318" t="n">
+        <v>340</v>
+      </c>
+      <c r="K318" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Pull the reported aggregate lease-liability balance for the same fiscal period.|Classification as operating vs financial liability is a separate Accounting Judgment.|This is not an ROU asset, lease payment, commitment, or amortization schedule.</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link</t>
+        </is>
+      </c>
+      <c r="Q318" t="n">
+        <v>87</v>
+      </c>
+      <c r="R318" t="n">
+        <v>2</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20241231</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>318</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Lease Liability</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Link the reported aggregate lease-liability balance.</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>E55</t>
+        </is>
+      </c>
+      <c r="I319">
+        <f>'Balance Sheet'!E16</f>
+        <v/>
+      </c>
+      <c r="J319" t="n">
+        <v>360</v>
+      </c>
+      <c r="K319" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Pull the reported aggregate lease-liability balance for the same fiscal period.|Classification as operating vs financial liability is a separate Accounting Judgment.|This is not an ROU asset, lease payment, commitment, or amortization schedule.</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link</t>
+        </is>
+      </c>
+      <c r="Q319" t="n">
+        <v>87</v>
+      </c>
+      <c r="R319" t="n">
+        <v>3</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20251231</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>319</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Lease Liability</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Link the reported aggregate lease-liability balance.</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>F55</t>
+        </is>
+      </c>
+      <c r="I320">
+        <f>'Balance Sheet'!F16</f>
+        <v/>
+      </c>
+      <c r="J320" t="n">
+        <v>380</v>
+      </c>
+      <c r="K320" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Pull the reported aggregate lease-liability balance for the same fiscal period.|Classification as operating vs financial liability is a separate Accounting Judgment.|This is not an ROU asset, lease payment, commitment, or amortization schedule.</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link</t>
+        </is>
+      </c>
+      <c r="Q320" t="n">
+        <v>87</v>
+      </c>
+      <c r="R320" t="n">
+        <v>4</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>lease_liability_to_revenue__20211231</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>320</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Reported lease liability divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_to_revenue.2021-12-31</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>B56</t>
+        </is>
+      </c>
+      <c r="I321">
+        <f>IF('Condensed Financials'!B19=0,NA(),B55/'Condensed Financials'!B19)</f>
+        <v/>
+      </c>
+      <c r="J321" t="n">
+        <v>0.03529411764705882</v>
+      </c>
+      <c r="K321" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20211231,revenue_link__20211231</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue = reported lease liability / Revenue.|A zero Revenue denominator makes the ratio undefined (#N/A).|The ratio uses the reported balance, not the reformulated classification treatment.</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>lease_liability_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q321" t="n">
+        <v>88</v>
+      </c>
+      <c r="R321" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>lease_liability_to_revenue__20221231</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>321</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Reported lease liability divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_to_revenue.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>C56</t>
+        </is>
+      </c>
+      <c r="I322">
+        <f>IF('Condensed Financials'!C19=0,NA(),C55/'Condensed Financials'!C19)</f>
+        <v/>
+      </c>
+      <c r="J322" t="n">
+        <v>0.03478260869565217</v>
+      </c>
+      <c r="K322" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20221231,revenue_link__20221231</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue = reported lease liability / Revenue.|A zero Revenue denominator makes the ratio undefined (#N/A).|The ratio uses the reported balance, not the reformulated classification treatment.</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>lease_liability_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q322" t="n">
+        <v>88</v>
+      </c>
+      <c r="R322" t="n">
+        <v>1</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>lease_liability_to_revenue__20231231</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>322</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Reported lease liability divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_to_revenue.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>D56</t>
+        </is>
+      </c>
+      <c r="I323">
+        <f>IF('Condensed Financials'!D19=0,NA(),D55/'Condensed Financials'!D19)</f>
+        <v/>
+      </c>
+      <c r="J323" t="n">
+        <v>0.03366336633663367</v>
+      </c>
+      <c r="K323" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20231231,revenue_link__20231231</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue = reported lease liability / Revenue.|A zero Revenue denominator makes the ratio undefined (#N/A).|The ratio uses the reported balance, not the reformulated classification treatment.</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>lease_liability_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q323" t="n">
+        <v>88</v>
+      </c>
+      <c r="R323" t="n">
+        <v>2</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>lease_liability_to_revenue__20241231</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>323</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Reported lease liability divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_to_revenue.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>E56</t>
+        </is>
+      </c>
+      <c r="I324">
+        <f>IF('Condensed Financials'!E19=0,NA(),E55/'Condensed Financials'!E19)</f>
+        <v/>
+      </c>
+      <c r="J324" t="n">
+        <v>0.03214285714285714</v>
+      </c>
+      <c r="K324" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20241231,revenue_link__20241231</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue = reported lease liability / Revenue.|A zero Revenue denominator makes the ratio undefined (#N/A).|The ratio uses the reported balance, not the reformulated classification treatment.</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>lease_liability_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q324" t="n">
+        <v>88</v>
+      </c>
+      <c r="R324" t="n">
+        <v>3</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>lease_liability_to_revenue__20251231</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>324</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Reported lease liability divided by Revenue.</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_to_revenue.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>F56</t>
+        </is>
+      </c>
+      <c r="I325">
+        <f>IF('Condensed Financials'!F19=0,NA(),F55/'Condensed Financials'!F19)</f>
+        <v/>
+      </c>
+      <c r="J325" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="K325" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20251231,revenue_link__20251231</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue = reported lease liability / Revenue.|A zero Revenue denominator makes the ratio undefined (#N/A).|The ratio uses the reported balance, not the reformulated classification treatment.</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>lease_liability_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q325" t="n">
+        <v>88</v>
+      </c>
+      <c r="R325" t="n">
+        <v>4</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>lease_liability_change__20221231</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>325</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Change in Lease Liability</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Current lease liability minus prior lease liability.</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_change.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>C57</t>
+        </is>
+      </c>
+      <c r="I326">
+        <f>C55-B55</f>
+        <v/>
+      </c>
+      <c r="J326" t="n">
+        <v>20</v>
+      </c>
+      <c r="K326" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20221231,lease_liability_source_link__20211231</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Change in Lease Liability = Current − Prior reported lease liability.|Balance change is not rent growth, lease cash payments, or ROU-asset growth.</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>lease_liability_change</t>
+        </is>
+      </c>
+      <c r="Q326" t="n">
+        <v>89</v>
+      </c>
+      <c r="R326" t="n">
+        <v>1</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>lease_liability_change__20231231</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>326</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Change in Lease Liability</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Current lease liability minus prior lease liability.</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_change.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
+      <c r="I327">
+        <f>D55-C55</f>
+        <v/>
+      </c>
+      <c r="J327" t="n">
+        <v>20</v>
+      </c>
+      <c r="K327" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20231231,lease_liability_source_link__20221231</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Change in Lease Liability = Current − Prior reported lease liability.|Balance change is not rent growth, lease cash payments, or ROU-asset growth.</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>lease_liability_change</t>
+        </is>
+      </c>
+      <c r="Q327" t="n">
+        <v>89</v>
+      </c>
+      <c r="R327" t="n">
+        <v>2</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>lease_liability_change__20241231</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>327</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Change in Lease Liability</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Current lease liability minus prior lease liability.</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_change.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>E57</t>
+        </is>
+      </c>
+      <c r="I328">
+        <f>E55-D55</f>
+        <v/>
+      </c>
+      <c r="J328" t="n">
+        <v>20</v>
+      </c>
+      <c r="K328" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20241231,lease_liability_source_link__20231231</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Change in Lease Liability = Current − Prior reported lease liability.|Balance change is not rent growth, lease cash payments, or ROU-asset growth.</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>lease_liability_change</t>
+        </is>
+      </c>
+      <c r="Q328" t="n">
+        <v>89</v>
+      </c>
+      <c r="R328" t="n">
+        <v>3</v>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>lease_liability_change__20251231</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>328</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Change in Lease Liability</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Current lease liability minus prior lease liability.</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_change.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>F57</t>
+        </is>
+      </c>
+      <c r="I329">
+        <f>F55-E55</f>
+        <v/>
+      </c>
+      <c r="J329" t="n">
+        <v>20</v>
+      </c>
+      <c r="K329" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20251231,lease_liability_source_link__20241231</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Change in Lease Liability = Current − Prior reported lease liability.|Balance change is not rent growth, lease cash payments, or ROU-asset growth.</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>lease_liability_change</t>
+        </is>
+      </c>
+      <c r="Q329" t="n">
+        <v>89</v>
+      </c>
+      <c r="R329" t="n">
+        <v>4</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>lease_liability_growth__20221231</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>329</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Lease Liability Growth</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Percentage change in reported lease liability.</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_growth.2022-12-31</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>C58</t>
+        </is>
+      </c>
+      <c r="I330">
+        <f>IF(B55=0,NA(),C55/B55-1)</f>
+        <v/>
+      </c>
+      <c r="J330" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="K330" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20221231,lease_liability_source_link__20211231</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Lease Liability Growth = Current / Prior − 1.|A zero prior lease-liability balance makes percentage growth undefined (#N/A).|Balance growth is not rent growth, lease cash payments, commitments, or ROU-asset growth.</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>lease_liability_growth</t>
+        </is>
+      </c>
+      <c r="Q330" t="n">
+        <v>90</v>
+      </c>
+      <c r="R330" t="n">
+        <v>1</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>lease_liability_growth__20231231</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>330</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Lease Liability Growth</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Percentage change in reported lease liability.</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_growth.2023-12-31</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>D58</t>
+        </is>
+      </c>
+      <c r="I331">
+        <f>IF(C55=0,NA(),D55/C55-1)</f>
+        <v/>
+      </c>
+      <c r="J331" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="K331" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20231231,lease_liability_source_link__20221231</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Lease Liability Growth = Current / Prior − 1.|A zero prior lease-liability balance makes percentage growth undefined (#N/A).|Balance growth is not rent growth, lease cash payments, commitments, or ROU-asset growth.</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>lease_liability_growth</t>
+        </is>
+      </c>
+      <c r="Q331" t="n">
+        <v>90</v>
+      </c>
+      <c r="R331" t="n">
+        <v>2</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>lease_liability_growth__20241231</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>331</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Lease Liability Growth</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Percentage change in reported lease liability.</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_growth.2024-12-31</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>E58</t>
+        </is>
+      </c>
+      <c r="I332">
+        <f>IF(D55=0,NA(),E55/D55-1)</f>
+        <v/>
+      </c>
+      <c r="J332" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="K332" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20241231,lease_liability_source_link__20231231</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Lease Liability Growth = Current / Prior − 1.|A zero prior lease-liability balance makes percentage growth undefined (#N/A).|Balance growth is not rent growth, lease cash payments, commitments, or ROU-asset growth.</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>lease_liability_growth</t>
+        </is>
+      </c>
+      <c r="Q332" t="n">
+        <v>90</v>
+      </c>
+      <c r="R332" t="n">
+        <v>3</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>lease_liability_growth__20251231</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>332</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Lease Liability Growth</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Percentage change in reported lease liability.</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>lease_liability.lease_liability_growth.2025-12-31</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>lease_liability</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>F58</t>
+        </is>
+      </c>
+      <c r="I333">
+        <f>IF(E55=0,NA(),F55/E55-1)</f>
+        <v/>
+      </c>
+      <c r="J333" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="K333" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>lease_liability_source_link__20251231,lease_liability_source_link__20241231</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Lease Liability Growth = Current / Prior − 1.|A zero prior lease-liability balance makes percentage growth undefined (#N/A).|Balance growth is not rent growth, lease cash payments, commitments, or ROU-asset growth.</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>lease_liability_growth</t>
+        </is>
+      </c>
+      <c r="Q333" t="n">
+        <v>90</v>
+      </c>
+      <c r="R333" t="n">
+        <v>4</v>
+      </c>
+      <c r="S333" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
@@ -30454,7 +32097,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"base_classification_overrides":{},"judgment_bindings":[{"allowed_treatments":["Operating Long-Term Liability","Financial Liability"],"case_id":"classification::concept=lease_liability|label=operating lease liabilities","line_identity":"concept=lease_liability|label=operating lease liabilities","order":1,"override_selector":"concept:lease_liability","reference_treatment":"Operating Long-Term Liability","worksheet_row":5}],"modeled_periods":["2021-12-31","2022-12-31","2023-12-31","2024-12-31","2025-12-31"],"normalization_bindings":[{"allowed_treatments":["Non-recurring","Recurring"],"case_id":"normalization::concept=restructuring_expense|label=restructuring expense","line_identity":"concept=restructuring_expense|label=restructuring expense","order":1,"reference_treatment":"Non-recurring","scope":"operating_pretax_effective_tax","source_selector":"concept:restructuring_expense","worksheet_row":5}],"schema_version":2,"source_payload":{"balance_sheet":[{"concept":"","label":"Cash and cash equivalents","values":{"2021-12-31":1200.0,"2022-12-31":1350.0,"2023-12-31":1500.0,"2024-12-31":1680.0,"2025-12-31":1850.0}},{"concept":"","label":"Trade receivables","values":{"2021-12-31":850.0,"2022-12-31":920.0,"2023-12-31":1010.0,"2024-12-31":1120.0,"2025-12-31":1250.0}},{"concept":"","label":"Inventories","values":{"2021-12-31":680.0,"2022-12-31":736.0,"2023-12-31":808.0,"2024-12-31":896.0,"2025-12-31":1000.0}},{"concept":"","label":"Property, plant and equipment","values":{"2021-12-31":3200.0,"2022-12-31":3400.0,"2023-12-31":3600.0,"2024-12-31":3800.0,"2025-12-31":4000.0}},{"concept":"","label":"Goodwill","values":{"2021-12-31":900.0,"2022-12-31":900.0,"2023-12-31":900.0,"2024-12-31":900.0,"2025-12-31":900.0}},{"concept":"","label":"Other non-current assets","values":{"2021-12-31":1670.0,"2022-12-31":1894.0,"2023-12-31":2282.0,"2024-12-31":2804.0,"2025-12-31":3500.0}},{"concept":"","label":"Total assets","values":{"2021-12-31":8500.0,"2022-12-31":9200.0,"2023-12-31":10100.0,"2024-12-31":11200.0,"2025-12-31":12500.0}},{"concept":"","label":"Trade payables","values":{"2021-12-31":595.0,"2022-12-31":644.0,"2023-12-31":707.0,"2024-12-31":784.0,"2025-12-31":875.0}},{"concept":"","label":"Bank borrowings","values":{"2021-12-31":1500.0,"2022-12-31":1400.0,"2023-12-31":1300.0,"2024-12-31":1200.0,"2025-12-31":1100.0}},{"concept":"lease_liability","label":"Operating lease liabilities","values":{"2021-12-31":300.0,"2022-12-31":320.0,"2023-12-31":340.0,"2024-12-31":360.0,"2025-12-31":380.0}},{"concept":"","label":"Other non-current liabilities","values":{"2021-12-31":1005.0,"2022-12-31":1136.0,"2023-12-31":1253.0,"2024-12-31":1356.0,"2025-12-31":1445.0}},{"concept":"","label":"Total liabilities","values":{"2021-12-31":3400.0,"2022-12-31":3500.0,"2023-12-31":3600.0,"2024-12-31":3700.0,"2025-12-31":3800.0}},{"concept":"","label":"Share capital and reserves","values":{"2021-12-31":5100.0,"2022-12-31":5700.0,"2023-12-31":6500.0,"2024-12-31":7500.0,"2025-12-31":8700.0}},{"concept":"","label":"Total equity","values":{"2021-12-31":5100.0,"2022-12-31":5700.0,"2023-12-31":6500.0,"2024-12-31":7500.0,"2025-12-31":8700.0}}],"cash_flow":[{"concept":"","label":"Profit for the year","values":{"2021-12-31":2760.0,"2022-12-31":2988.0,"2023-12-31":3283.0,"2024-12-31":3644.0,"2025-12-31":4072.0}},{"concept":"","label":"Depreciation and amortisation","values":{"2021-12-31":340.0,"2022-12-31":368.0,"2023-12-31":404.0,"2024-12-31":448.0,"2025-12-31":500.0}},{"concept":"","label":"Net cash from operating activities","values":{"2021-12-31":1450.0,"2022-12-31":1600.0,"2023-12-31":1750.0,"2024-12-31":1930.0,"2025-12-31":2070.0}},{"concept":"","label":"Net cash used in investing activities","values":{"2021-12-31":-800.0,"2022-12-31":-850.0,"2023-12-31":-900.0,"2024-12-31":-950.0,"2025-12-31":-1000.0}},{"concept":"","label":"Net cash from financing activities","values":{"2021-12-31":-500.0,"2022-12-31":-600.0,"2023-12-31":-700.0,"2024-12-31":-800.0,"2025-12-31":-900.0}},{"concept":"","label":"Net change in cash and cash equivalents","values":{"2021-12-31":150.0,"2022-12-31":150.0,"2023-12-31":150.0,"2024-12-31":180.0,"2025-12-31":170.0}}],"company_name":"Demo Holdings Limited","currency":"HKD","historical_shares":null,"income_statement":[{"concept":"","label":"Revenue","values":{"2021-12-31":8500.0,"2022-12-31":9200.0,"2023-12-31":10100.0,"2024-12-31":11200.0,"2025-12-31":12500.0}},{"concept":"","label":"Cost of sales","values":{"2021-12-31":-3400.0,"2022-12-31":-3680.0,"2023-12-31":-4040.0,"2024-12-31":-4480.0,"2025-12-31":-5000.0}},{"concept":"","label":"Gross profit","values":{"2021-12-31":5100.0,"2022-12-31":5520.0,"2023-12-31":6060.0,"2024-12-31":6720.0,"2025-12-31":7500.0}},{"concept":"","label":"Administrative expenses","values":{"2021-12-31":-1700.0,"2022-12-31":-1840.0,"2023-12-31":-1820.0,"2024-12-31":-2240.0,"2025-12-31":-2500.0}},{"concept":"restructuring_expense","label":"Restructuring expense","values":{"2021-12-31":0.0,"2022-12-31":0.0,"2023-12-31":-200.0,"2024-12-31":0.0,"2025-12-31":0.0}},{"concept":"","label":"Operating profit","values":{"2021-12-31":3400.0,"2022-12-31":3680.0,"2023-12-31":4040.0,"2024-12-31":4480.0,"2025-12-31":5000.0}},{"concept":"","label":"Finance costs","values":{"2021-12-31":-120.0,"2022-12-31":-130.0,"2023-12-31":-140.0,"2024-12-31":-150.0,"2025-12-31":-160.0}},{"concept":"","label":"Finance income","values":{"2021-12-31":45.0,"2022-12-31":50.0,"2023-12-31":55.0,"2024-12-31":60.0,"2025-12-31":65.0}},{"concept":"","label":"Profit before tax","values":{"2021-12-31":3325.0,"2022-12-31":3600.0,"2023-12-31":3955.0,"2024-12-31":4390.0,"2025-12-31":4905.0}},{"concept":"","label":"Income tax expense","values":{"2021-12-31":-565.0,"2022-12-31":-612.0,"2023-12-31":-672.0,"2024-12-31":-746.0,"2025-12-31":-833.0}},{"concept":"","label":"Profit for the year","values":{"2021-12-31":2760.0,"2022-12-31":2988.0,"2023-12-31":3283.0,"2024-12-31":3644.0,"2025-12-31":4072.0}}],"jurisdiction":"HK","periods":[{"end_date":"2021-12-31","is_interim":false,"label":"FY2021"},{"end_date":"2022-12-31","is_interim":false,"label":"FY2022"},{"end_date":"2023-12-31","is_interim":false,"label":"FY2023"},{"end_date":"2024-12-31","is_interim":false,"label":"FY2024"},{"end_date":"2025-12-31","is_interim":false,"label":"FY2025"}],"stock_code":"1234.HK","ticker":"DEMO","units":"HKD in Millions"}}</t>
+          <t>{"base_classification_overrides":{},"judgment_bindings":[{"allowed_treatments":["Operating Long-Term Liability","Financial Liability"],"case_id":"classification::concept=lease_liability|label=operating lease liabilities","line_identity":"concept=lease_liability|label=operating lease liabilities","order":1,"override_selector":"identity:concept=lease_liability|label=operating lease liabilities","reference_treatment":"Operating Long-Term Liability","worksheet_row":5}],"modeled_periods":["2021-12-31","2022-12-31","2023-12-31","2024-12-31","2025-12-31"],"normalization_bindings":[{"allowed_treatments":["Non-recurring","Recurring"],"case_id":"normalization::concept=restructuring_expense|label=restructuring expense","line_identity":"concept=restructuring_expense|label=restructuring expense","order":1,"reference_treatment":"Non-recurring","scope":"operating_pretax_effective_tax","source_selector":"concept:restructuring_expense","worksheet_row":5}],"schema_version":2,"source_payload":{"balance_sheet":[{"concept":"","label":"Cash and cash equivalents","values":{"2021-12-31":1200.0,"2022-12-31":1350.0,"2023-12-31":1500.0,"2024-12-31":1680.0,"2025-12-31":1850.0}},{"concept":"","label":"Trade receivables","values":{"2021-12-31":850.0,"2022-12-31":920.0,"2023-12-31":1010.0,"2024-12-31":1120.0,"2025-12-31":1250.0}},{"concept":"","label":"Inventories","values":{"2021-12-31":680.0,"2022-12-31":736.0,"2023-12-31":808.0,"2024-12-31":896.0,"2025-12-31":1000.0}},{"concept":"","label":"Property, plant and equipment","values":{"2021-12-31":3200.0,"2022-12-31":3400.0,"2023-12-31":3600.0,"2024-12-31":3800.0,"2025-12-31":4000.0}},{"concept":"","label":"Goodwill","values":{"2021-12-31":900.0,"2022-12-31":900.0,"2023-12-31":900.0,"2024-12-31":900.0,"2025-12-31":900.0}},{"concept":"","label":"Other non-current assets","values":{"2021-12-31":1670.0,"2022-12-31":1894.0,"2023-12-31":2282.0,"2024-12-31":2804.0,"2025-12-31":3500.0}},{"concept":"","label":"Total assets","values":{"2021-12-31":8500.0,"2022-12-31":9200.0,"2023-12-31":10100.0,"2024-12-31":11200.0,"2025-12-31":12500.0}},{"concept":"","label":"Trade payables","values":{"2021-12-31":595.0,"2022-12-31":644.0,"2023-12-31":707.0,"2024-12-31":784.0,"2025-12-31":875.0}},{"concept":"","label":"Bank borrowings","values":{"2021-12-31":1500.0,"2022-12-31":1400.0,"2023-12-31":1300.0,"2024-12-31":1200.0,"2025-12-31":1100.0}},{"concept":"lease_liability","label":"Operating lease liabilities","values":{"2021-12-31":300.0,"2022-12-31":320.0,"2023-12-31":340.0,"2024-12-31":360.0,"2025-12-31":380.0}},{"concept":"","label":"Other non-current liabilities","values":{"2021-12-31":1005.0,"2022-12-31":1136.0,"2023-12-31":1253.0,"2024-12-31":1356.0,"2025-12-31":1445.0}},{"concept":"","label":"Total liabilities","values":{"2021-12-31":3400.0,"2022-12-31":3500.0,"2023-12-31":3600.0,"2024-12-31":3700.0,"2025-12-31":3800.0}},{"concept":"","label":"Share capital and reserves","values":{"2021-12-31":5100.0,"2022-12-31":5700.0,"2023-12-31":6500.0,"2024-12-31":7500.0,"2025-12-31":8700.0}},{"concept":"","label":"Total equity","values":{"2021-12-31":5100.0,"2022-12-31":5700.0,"2023-12-31":6500.0,"2024-12-31":7500.0,"2025-12-31":8700.0}}],"cash_flow":[{"concept":"","label":"Profit for the year","values":{"2021-12-31":2760.0,"2022-12-31":2988.0,"2023-12-31":3283.0,"2024-12-31":3644.0,"2025-12-31":4072.0}},{"concept":"","label":"Depreciation and amortisation","values":{"2021-12-31":340.0,"2022-12-31":368.0,"2023-12-31":404.0,"2024-12-31":448.0,"2025-12-31":500.0}},{"concept":"","label":"Net cash from operating activities","values":{"2021-12-31":1450.0,"2022-12-31":1600.0,"2023-12-31":1750.0,"2024-12-31":1930.0,"2025-12-31":2070.0}},{"concept":"","label":"Net cash used in investing activities","values":{"2021-12-31":-800.0,"2022-12-31":-850.0,"2023-12-31":-900.0,"2024-12-31":-950.0,"2025-12-31":-1000.0}},{"concept":"","label":"Net cash from financing activities","values":{"2021-12-31":-500.0,"2022-12-31":-600.0,"2023-12-31":-700.0,"2024-12-31":-800.0,"2025-12-31":-900.0}},{"concept":"","label":"Net change in cash and cash equivalents","values":{"2021-12-31":150.0,"2022-12-31":150.0,"2023-12-31":150.0,"2024-12-31":180.0,"2025-12-31":170.0}}],"company_name":"Demo Holdings Limited","currency":"HKD","historical_shares":null,"income_statement":[{"concept":"","label":"Revenue","values":{"2021-12-31":8500.0,"2022-12-31":9200.0,"2023-12-31":10100.0,"2024-12-31":11200.0,"2025-12-31":12500.0}},{"concept":"","label":"Cost of sales","values":{"2021-12-31":-3400.0,"2022-12-31":-3680.0,"2023-12-31":-4040.0,"2024-12-31":-4480.0,"2025-12-31":-5000.0}},{"concept":"","label":"Gross profit","values":{"2021-12-31":5100.0,"2022-12-31":5520.0,"2023-12-31":6060.0,"2024-12-31":6720.0,"2025-12-31":7500.0}},{"concept":"","label":"Administrative expenses","values":{"2021-12-31":-1700.0,"2022-12-31":-1840.0,"2023-12-31":-1820.0,"2024-12-31":-2240.0,"2025-12-31":-2500.0}},{"concept":"restructuring_expense","label":"Restructuring expense","values":{"2021-12-31":0.0,"2022-12-31":0.0,"2023-12-31":-200.0,"2024-12-31":0.0,"2025-12-31":0.0}},{"concept":"","label":"Operating profit","values":{"2021-12-31":3400.0,"2022-12-31":3680.0,"2023-12-31":4040.0,"2024-12-31":4480.0,"2025-12-31":5000.0}},{"concept":"","label":"Finance costs","values":{"2021-12-31":-120.0,"2022-12-31":-130.0,"2023-12-31":-140.0,"2024-12-31":-150.0,"2025-12-31":-160.0}},{"concept":"","label":"Finance income","values":{"2021-12-31":45.0,"2022-12-31":50.0,"2023-12-31":55.0,"2024-12-31":60.0,"2025-12-31":65.0}},{"concept":"","label":"Profit before tax","values":{"2021-12-31":3325.0,"2022-12-31":3600.0,"2023-12-31":3955.0,"2024-12-31":4390.0,"2025-12-31":4905.0}},{"concept":"","label":"Income tax expense","values":{"2021-12-31":-565.0,"2022-12-31":-612.0,"2023-12-31":-672.0,"2024-12-31":-746.0,"2025-12-31":-833.0}},{"concept":"","label":"Profit for the year","values":{"2021-12-31":2760.0,"2022-12-31":2988.0,"2023-12-31":3283.0,"2024-12-31":3644.0,"2025-12-31":4072.0}}],"jurisdiction":"HK","periods":[{"end_date":"2021-12-31","is_interim":false,"label":"FY2021"},{"end_date":"2022-12-31","is_interim":false,"label":"FY2022"},{"end_date":"2023-12-31","is_interim":false,"label":"FY2023"},{"end_date":"2024-12-31","is_interim":false,"label":"FY2024"},{"end_date":"2025-12-31","is_interim":false,"label":"FY2025"}],"stock_code":"1234.HK","ticker":"DEMO","units":"HKD in Millions"}}</t>
         </is>
       </c>
     </row>
@@ -32428,7 +34071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -33587,6 +35230,124 @@
       </c>
       <c r="F52" s="9">
         <f>IF(OR(ISNA(F47),ISNA(F48)),"N/A",IF(ABS(F47*F48-1)&lt;0.0000001,"OK","CHECK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>LEASE LIABILITY CONTEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Lease Liability</t>
+        </is>
+      </c>
+      <c r="B55" s="14">
+        <f>'Balance Sheet'!B16</f>
+        <v/>
+      </c>
+      <c r="C55" s="14">
+        <f>'Balance Sheet'!C16</f>
+        <v/>
+      </c>
+      <c r="D55" s="14">
+        <f>'Balance Sheet'!D16</f>
+        <v/>
+      </c>
+      <c r="E55" s="14">
+        <f>'Balance Sheet'!E16</f>
+        <v/>
+      </c>
+      <c r="F55" s="14">
+        <f>'Balance Sheet'!F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Lease Liability / Revenue</t>
+        </is>
+      </c>
+      <c r="B56" s="13">
+        <f>IF('Condensed Financials'!B19=0,NA(),B55/'Condensed Financials'!B19)</f>
+        <v/>
+      </c>
+      <c r="C56" s="13">
+        <f>IF('Condensed Financials'!C19=0,NA(),C55/'Condensed Financials'!C19)</f>
+        <v/>
+      </c>
+      <c r="D56" s="13">
+        <f>IF('Condensed Financials'!D19=0,NA(),D55/'Condensed Financials'!D19)</f>
+        <v/>
+      </c>
+      <c r="E56" s="13">
+        <f>IF('Condensed Financials'!E19=0,NA(),E55/'Condensed Financials'!E19)</f>
+        <v/>
+      </c>
+      <c r="F56" s="13">
+        <f>IF('Condensed Financials'!F19=0,NA(),F55/'Condensed Financials'!F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Change in Lease Liability</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="14">
+        <f>C55-B55</f>
+        <v/>
+      </c>
+      <c r="D57" s="14">
+        <f>D55-C55</f>
+        <v/>
+      </c>
+      <c r="E57" s="14">
+        <f>E55-D55</f>
+        <v/>
+      </c>
+      <c r="F57" s="14">
+        <f>F55-E55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Lease Liability Growth</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="13">
+        <f>IF(B55=0,NA(),C55/B55-1)</f>
+        <v/>
+      </c>
+      <c r="D58" s="13">
+        <f>IF(C55=0,NA(),D55/C55-1)</f>
+        <v/>
+      </c>
+      <c r="E58" s="13">
+        <f>IF(D55=0,NA(),E55/D55-1)</f>
+        <v/>
+      </c>
+      <c r="F58" s="13">
+        <f>IF(E55=0,NA(),F55/E55-1)</f>
         <v/>
       </c>
     </row>
